--- a/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/env_ord_pca/site_pca_scores.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/env_ord_pca/site_pca_scores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F234"/>
+  <dimension ref="A1:F311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,5127 +463,6821 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>003ABC</t>
+          <t>DR-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.760459261603462</v>
+        <v>-0.3337237858445243</v>
       </c>
       <c r="C2" t="n">
-        <v>1.072515738245783</v>
+        <v>-2.245045502185692</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4563340530211494</v>
+        <v>-0.3042877657286648</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2928730810485719</v>
+        <v>-0.1162669518451237</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6281904079461073</v>
+        <v>-0.5836857093699168</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.085939220724867</v>
+        <v>0.4445439172622528</v>
       </c>
       <c r="C3" t="n">
-        <v>1.483022290322316</v>
+        <v>-2.025909344919296</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.037294047756706</v>
+        <v>-0.8131183908081855</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002157784770268469</v>
+        <v>-0.5726541964526596</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7197982079184838</v>
+        <v>-0.5938700612604154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>005ABC</t>
+          <t>DR-04</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.524164480210179</v>
+        <v>0.2127926180902411</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3486868380731384</v>
+        <v>-0.8563690485007667</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.057979784536794</v>
+        <v>-1.090427349159632</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.07862737648569744</v>
+        <v>-0.4663475806190294</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.340301519324706</v>
+        <v>-1.202090516154346</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>007ABC</t>
+          <t>DR-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6348874980322061</v>
+        <v>0.3209319508754588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8339446242891954</v>
+        <v>-1.422832130271151</v>
       </c>
       <c r="D5" t="n">
-        <v>1.453184083905604</v>
+        <v>1.545797628498304</v>
       </c>
       <c r="E5" t="n">
-        <v>1.257390813778296</v>
+        <v>1.203321942921093</v>
       </c>
       <c r="F5" t="n">
-        <v>0.122850427073412</v>
+        <v>-0.1909545254084482</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>008A</t>
+          <t>DR-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5697189825178678</v>
+        <v>1.383734320566489</v>
       </c>
       <c r="C6" t="n">
-        <v>2.433562714904844</v>
+        <v>-2.284151951844749</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.537658467411933</v>
+        <v>-1.079136361506062</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2606453387781315</v>
+        <v>-0.9716209803862238</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.06708347652472951</v>
+        <v>0.1171914108436937</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>009B</t>
+          <t>DR-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.793159004469335</v>
+        <v>0.451092224784516</v>
       </c>
       <c r="C7" t="n">
-        <v>1.088536022846752</v>
+        <v>-1.608353648484044</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7554143186349184</v>
+        <v>-0.625834219183134</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2625958540516831</v>
+        <v>-0.2047688109052552</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7811619753702507</v>
+        <v>-0.7308867036100939</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.2247248418297918</v>
+        <v>-0.2146059976753595</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.061270259706117</v>
+        <v>0.6779325495695171</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7963700226804551</v>
+        <v>-0.9317715897777794</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3367233578898299</v>
+        <v>0.1034827116389563</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1500078601511261</v>
+        <v>0.2533717872991044</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.0952502001652358</v>
+        <v>-0.3328707676953506</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.175582311312027</v>
+        <v>0.4880741426413119</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1974145590467175</v>
+        <v>-0.3476353526166221</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4773087039563514</v>
+        <v>1.078514918112137</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7038705898696813</v>
+        <v>0.6027536497373017</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>012A</t>
+          <t>DR-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.230447533763279</v>
+        <v>1.079928686847442</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.3018342123016511</v>
+        <v>0.744938301910731</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.142843076349427</v>
+        <v>-1.140125226206459</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.03905765501346715</v>
+        <v>0.2322684721858061</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5408868358999198</v>
+        <v>0.5809416356062667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>013A</t>
+          <t>DR-32</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.268429965647923</v>
+        <v>0.8808883240524829</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.6069072304293033</v>
+        <v>1.046767444611538</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6952041701609271</v>
+        <v>-0.7776050230376488</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1494346080180467</v>
+        <v>0.1686099889842374</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1826973638658348</v>
+        <v>0.2198331188322381</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>014B</t>
+          <t>DR-43</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3327897274546787</v>
+        <v>-0.6839598143031853</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.208930585458769</v>
+        <v>0.1766643228796565</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.07577017857725879</v>
+        <v>-0.200855541810282</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6490233491030789</v>
+        <v>1.345174431494338</v>
       </c>
       <c r="F12" t="n">
-        <v>1.070134461608113</v>
+        <v>0.9296608872268332</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>015C</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4143362638611745</v>
+        <v>-0.9237545416566424</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.445732542193148</v>
+        <v>0.4094374411616865</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4405892413232317</v>
+        <v>-0.6183210639462634</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0777549715896199</v>
+        <v>0.7279726400571018</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5635046323187478</v>
+        <v>0.5683864784338547</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-65</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0360297395753441</v>
+        <v>-0.2971329391052679</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.048511943287794</v>
+        <v>0.4393502126529757</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7384881586374</v>
+        <v>-1.006303584143964</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.08457071844006124</v>
+        <v>0.006218699383337061</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.185519429612754</v>
+        <v>-1.091824704594155</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>017B</t>
+          <t>DR-76</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.731163039793023</v>
+        <v>0.3209438770051304</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.9080649920710504</v>
+        <v>0.7980417747400094</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4439813706849591</v>
+        <v>-0.5831349672859568</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2233279739844563</v>
+        <v>0.6417958667542177</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2720545488767933</v>
+        <v>0.2319379818728064</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>018A</t>
+          <t>DR-87</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.000710440986054</v>
+        <v>-2.25102506887619</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.59018738891409</v>
+        <v>-0.6687556351877966</v>
       </c>
       <c r="D16" t="n">
-        <v>1.055448934790118</v>
+        <v>0.8349143873756409</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8562600732229484</v>
+        <v>1.640587399694101</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7016150230492357</v>
+        <v>0.4951323594677047</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>019B</t>
+          <t>DR-98</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.367699053603147</v>
+        <v>0.09245730411275224</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.843606250817422</v>
+        <v>0.5048857877146655</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0359541338958677</v>
+        <v>-0.1517176267215197</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3953137266223621</v>
+        <v>0.6843172099285048</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2769877680906596</v>
+        <v>-0.3579254415035997</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>021B</t>
+          <t>DR-109</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.634684739337405</v>
+        <v>-2.867227349353874</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.83056662262835</v>
+        <v>-0.8888573546923014</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1303380936948832</v>
+        <v>-0.09620985337734876</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3757567259921796</v>
+        <v>1.155933927666968</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5937914084840642</v>
+        <v>0.5569224423787403</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>022B</t>
+          <t>DR-120</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.492114122974759</v>
+        <v>-1.690861821715036</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.53289198452771</v>
+        <v>-0.556032857517274</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9588110999915138</v>
+        <v>0.6931095162210431</v>
       </c>
       <c r="E19" t="n">
-        <v>1.551155354184751</v>
+        <v>2.234696413935328</v>
       </c>
       <c r="F19" t="n">
-        <v>0.582743963679878</v>
+        <v>0.2435810170644043</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>023C</t>
+          <t>DR-131</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.2355706684835448</v>
+        <v>-0.1054432541524284</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.163803093120319</v>
+        <v>0.6068316490886562</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4119348133717671</v>
+        <v>-0.7436583831159873</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3708853490091321</v>
+        <v>0.4592331979857186</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.318046851516162</v>
+        <v>-1.33553645495607</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>024C</t>
+          <t>DR-142</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.3071254310082703</v>
+        <v>-0.237593349821788</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.9494180591906782</v>
+        <v>0.6550957125030018</v>
       </c>
       <c r="D21" t="n">
-        <v>1.213106006417484</v>
+        <v>1.142146632220121</v>
       </c>
       <c r="E21" t="n">
-        <v>0.267679500468387</v>
+        <v>1.064063240393958</v>
       </c>
       <c r="F21" t="n">
-        <v>1.212844315331766</v>
+        <v>1.03837355352681</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>025B</t>
+          <t>DR-153</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.118674360955136</v>
+        <v>0.4106422874976088</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.362227386896286</v>
+        <v>1.326049051781</v>
       </c>
       <c r="D22" t="n">
-        <v>0.582337240318567</v>
+        <v>0.1845098340031011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7441817021707424</v>
+        <v>0.98598784516412</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.188680422573362</v>
+        <v>-1.369652659536979</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-160</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.874209073534214</v>
+        <v>-2.276082371446214</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.755936916098201</v>
+        <v>-0.2919744231204046</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1698362683868946</v>
+        <v>-0.1009205226674787</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.04422500016771162</v>
+        <v>0.5778272695599667</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1166644033148394</v>
+        <v>-0.07774792613316316</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>027B</t>
+          <t>DR-161</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.068843943447908</v>
+        <v>-0.1485003503871353</v>
       </c>
       <c r="C24" t="n">
-        <v>1.420500436155073</v>
+        <v>-3.201729892466798</v>
       </c>
       <c r="D24" t="n">
-        <v>1.367936180847687</v>
+        <v>1.476434345158902</v>
       </c>
       <c r="E24" t="n">
-        <v>2.715538468567189</v>
+        <v>2.2826965653964</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2145002235995541</v>
+        <v>-0.7472719620884765</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>029C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.94490867428891</v>
+        <v>-0.1546044139882345</v>
       </c>
       <c r="C25" t="n">
-        <v>1.529073680529186</v>
+        <v>-2.866765095816858</v>
       </c>
       <c r="D25" t="n">
-        <v>0.09076021798303377</v>
+        <v>0.3497311581480856</v>
       </c>
       <c r="E25" t="n">
-        <v>1.12805695772417</v>
+        <v>0.7693463738560155</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1801339134502016</v>
+        <v>0.01764545879266743</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.364459693828105</v>
+        <v>-1.420055418846305</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1383221447137846</v>
+        <v>-2.132481681489229</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4503698265385972</v>
+        <v>0.5332429736241113</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8852164702133893</v>
+        <v>1.099980755093351</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6711707141290442</v>
+        <v>0.5196970830450294</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>031A</t>
+          <t>DR-165</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.735871276740045</v>
+        <v>-1.995156508211895</v>
       </c>
       <c r="C27" t="n">
-        <v>1.532151924634059</v>
+        <v>-3.456170653917729</v>
       </c>
       <c r="D27" t="n">
-        <v>2.052888328941388</v>
+        <v>2.375302915702143</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.5834082597143999</v>
+        <v>-0.7622454101153067</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2031616224918642</v>
+        <v>-0.1234372561470373</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.497152431809525</v>
+        <v>-1.85328521273328</v>
       </c>
       <c r="C28" t="n">
-        <v>-1.742203191389269</v>
+        <v>-0.2548276111321526</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5026032274536371</v>
+        <v>0.1661401098780634</v>
       </c>
       <c r="E28" t="n">
-        <v>0.837510587079642</v>
+        <v>1.39080441699834</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2451027666952805</v>
+        <v>-0.3995071304907004</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>034C</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.224350406884099</v>
+        <v>-3.344172575457057</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.7770801867301466</v>
+        <v>0.5588939257139054</v>
       </c>
       <c r="D29" t="n">
-        <v>5.74450139854503</v>
+        <v>5.898816995845345</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.69758508384214</v>
+        <v>-3.388029718714151</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5732668870523578</v>
+        <v>1.101958422021615</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-169</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.417907551841708</v>
+        <v>-3.594648498074912</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.47966984132402</v>
+        <v>-1.143935343624181</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6473252391128484</v>
+        <v>0.56507731304187</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.341202107701283</v>
+        <v>-0.5376683061220121</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4491400405124371</v>
+        <v>0.7236635616549395</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-170</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.231324147092851</v>
+        <v>-1.317217898012056</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.189641733670749</v>
+        <v>-0.5414085817920391</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9592057054963837</v>
+        <v>0.7492070720888354</v>
       </c>
       <c r="E31" t="n">
-        <v>1.317639597579674</v>
+        <v>1.890175103127231</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4639779426679007</v>
+        <v>0.166949015121743</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>037B</t>
+          <t>DR-171</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.357837475995005</v>
+        <v>-1.39602975769141</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.8932596914993396</v>
+        <v>-0.7334964678682759</v>
       </c>
       <c r="D32" t="n">
-        <v>1.561359138415165</v>
+        <v>1.524345313522712</v>
       </c>
       <c r="E32" t="n">
-        <v>1.123103692256376</v>
+        <v>1.980113278375905</v>
       </c>
       <c r="F32" t="n">
-        <v>1.707004255363715</v>
+        <v>1.378112633888133</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>042C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.025662827026679</v>
+        <v>0.05637801497611056</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1596814503476174</v>
+        <v>1.615646362108692</v>
       </c>
       <c r="D33" t="n">
-        <v>5.291911507324982</v>
+        <v>5.305012897829111</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.049303710608802</v>
+        <v>-1.283007136339809</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.06199636885623884</v>
+        <v>-0.05904812918936286</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>043ABC</t>
+          <t>DR-176</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.617000543336297</v>
+        <v>-1.849204887339574</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.23053896351136</v>
+        <v>-0.6062007818875066</v>
       </c>
       <c r="D34" t="n">
-        <v>2.460200036827832</v>
+        <v>2.296788775372212</v>
       </c>
       <c r="E34" t="n">
-        <v>1.136265533214707</v>
+        <v>1.998581602930001</v>
       </c>
       <c r="F34" t="n">
-        <v>1.034882462025259</v>
+        <v>0.6649251092137709</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>044A</t>
+          <t>DR-177</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.07449228090638292</v>
+        <v>0.8853379318461326</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8470068555495568</v>
+        <v>-0.9889992513899069</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2556118030358802</v>
+        <v>-0.2462290855570355</v>
       </c>
       <c r="E35" t="n">
-        <v>0.5621940059247882</v>
+        <v>0.06892624804710949</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.276233786896756</v>
+        <v>-1.322132165670066</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>045B</t>
+          <t>DR-178</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6276871761726444</v>
+        <v>1.444306940332533</v>
       </c>
       <c r="C36" t="n">
-        <v>1.273981809325195</v>
+        <v>-0.5516348320054691</v>
       </c>
       <c r="D36" t="n">
-        <v>1.275248151776274</v>
+        <v>1.377188848018138</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1490766574231163</v>
+        <v>-0.2390931977913445</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.009122954465982</v>
+        <v>-1.103279302514564</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>047ABC</t>
+          <t>DR-180</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.917438536390483</v>
+        <v>-2.291549582373837</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.7428936822648559</v>
+        <v>-1.946485213148861</v>
       </c>
       <c r="D37" t="n">
-        <v>0.7056838757795788</v>
+        <v>0.5060752446368005</v>
       </c>
       <c r="E37" t="n">
-        <v>1.099177729269576</v>
+        <v>1.238650072644687</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6841233877932109</v>
+        <v>-0.8486503189548825</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>048C</t>
+          <t>DR-181</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.898925768023196</v>
+        <v>-0.7355633199037397</v>
       </c>
       <c r="C38" t="n">
-        <v>0.454620825963964</v>
+        <v>-2.204536856271038</v>
       </c>
       <c r="D38" t="n">
-        <v>0.06940358586476172</v>
+        <v>0.1645823366801542</v>
       </c>
       <c r="E38" t="n">
-        <v>1.426126901565803</v>
+        <v>1.454846659784181</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5673220114685179</v>
+        <v>0.3332941930913358</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>049A</t>
+          <t>DR-182</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.975796613640337</v>
+        <v>-1.419582868992835</v>
       </c>
       <c r="C39" t="n">
-        <v>1.285578786122167</v>
+        <v>-3.046141559972992</v>
       </c>
       <c r="D39" t="n">
-        <v>2.274421082879826</v>
+        <v>2.51706000755382</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4788516149586287</v>
+        <v>0.4069495538108604</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1495073799717594</v>
+        <v>-0.01388945237704302</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>052B</t>
+          <t>DR-184</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8836670497663567</v>
+        <v>-0.3340792019117788</v>
       </c>
       <c r="C40" t="n">
-        <v>1.071473375737182</v>
+        <v>-0.857569209905184</v>
       </c>
       <c r="D40" t="n">
-        <v>2.535238705848105</v>
+        <v>2.812234408384512</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.66676246050285</v>
+        <v>-1.498046914445597</v>
       </c>
       <c r="F40" t="n">
-        <v>0.08831186199882375</v>
+        <v>0.2565838054804285</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>054B</t>
+          <t>DR-186</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.082074977901326</v>
+        <v>-1.203268732829526</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.305833953315149</v>
+        <v>-0.3155301523852048</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9335208101832543</v>
+        <v>0.5570181631894487</v>
       </c>
       <c r="E41" t="n">
-        <v>1.199050570302356</v>
+        <v>1.414481674790527</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.14787521696726</v>
+        <v>-1.383379233185649</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>055C</t>
+          <t>DR-187</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.745919162056177</v>
+        <v>-1.44111874150389</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5842100880231808</v>
+        <v>-2.602159151198889</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3729621282359954</v>
+        <v>-0.2012568691134155</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3137755696360731</v>
+        <v>0.2817587249624924</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3260662636260234</v>
+        <v>0.3580520351158582</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>057C</t>
+          <t>DR-188</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.319369153919206</v>
+        <v>-1.565370045630775</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.1734257198897755</v>
+        <v>-1.851878148546176</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4793346179677741</v>
+        <v>0.4591804855010251</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7641510846562443</v>
+        <v>0.9361286508891979</v>
       </c>
       <c r="F43" t="n">
-        <v>0.08237688002662169</v>
+        <v>-0.03594894319761344</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-189</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.279610027834963</v>
+        <v>-0.1541223818357064</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6156061727102454</v>
+        <v>-1.851339290058803</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01830696423356028</v>
+        <v>0.09295510599383601</v>
       </c>
       <c r="E44" t="n">
-        <v>1.295357986760483</v>
+        <v>1.166423269786815</v>
       </c>
       <c r="F44" t="n">
-        <v>0.08080293527302879</v>
+        <v>-0.1272181659221163</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>059ABC</t>
+          <t>DR-190</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.933678593189763</v>
+        <v>1.698197927879475</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9018107888053886</v>
+        <v>-0.4231087094720952</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6062174135224001</v>
+        <v>0.5838371118518494</v>
       </c>
       <c r="E45" t="n">
-        <v>1.147896539394138</v>
+        <v>0.7159407018465753</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.116128063848993</v>
+        <v>-1.358783883803734</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-191</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.290926469900981</v>
+        <v>-1.26874091852714</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2556418024543486</v>
+        <v>-2.03272223694972</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4132418185702643</v>
+        <v>-0.3654563130765197</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1882792331832468</v>
+        <v>0.08330385682937022</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.3948488111042587</v>
+        <v>-0.3311017712660299</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-193</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-1.692695171493578</v>
+        <v>1.42723711032617</v>
       </c>
       <c r="C47" t="n">
-        <v>0.356365875916617</v>
+        <v>1.099458152348296</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9298569772859658</v>
+        <v>1.090547025678345</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.141478497269238</v>
+        <v>-0.762147397891736</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7146977297993332</v>
+        <v>0.8084952684589817</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>065C</t>
+          <t>DR-194</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-1.337713790404915</v>
+        <v>1.380305322394594</v>
       </c>
       <c r="C48" t="n">
-        <v>0.100643688416791</v>
+        <v>0.5554304287389616</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6980553316116445</v>
+        <v>-0.6379380350741268</v>
       </c>
       <c r="E48" t="n">
-        <v>0.07735616979903512</v>
+        <v>0.2634253240028517</v>
       </c>
       <c r="F48" t="n">
-        <v>0.552178765720138</v>
+        <v>0.5397099168505587</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-1.594076758658212</v>
+        <v>1.526341900742359</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2579393451162397</v>
+        <v>0.8075422400129743</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4005142363321069</v>
+        <v>-0.2615902198670493</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.5026017435615235</v>
+        <v>-0.2181421408525641</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8574017525672682</v>
+        <v>0.9197931980762241</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>067B</t>
+          <t>DR-196</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-1.404255595847981</v>
+        <v>0.8800902497781965</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.5112184744169651</v>
+        <v>1.256721444101669</v>
       </c>
       <c r="D50" t="n">
-        <v>1.037199447701812</v>
+        <v>0.9095894933383456</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.2520587189010308</v>
+        <v>0.06851099063993588</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.3176407165884601</v>
+        <v>-0.3681357818775862</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.184728986161671</v>
+        <v>-0.1552961635668193</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.4588280279785776</v>
+        <v>-0.1384408615873456</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.09142565514606558</v>
+        <v>-0.09691594153696551</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3439643350332284</v>
+        <v>0.7826445190420735</v>
       </c>
       <c r="F51" t="n">
-        <v>0.828936963332992</v>
+        <v>0.7533415880121554</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>069A</t>
+          <t>DR-198</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.999914889174814</v>
+        <v>1.865783150584077</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5069260141548551</v>
+        <v>1.050581070409434</v>
       </c>
       <c r="D52" t="n">
-        <v>0.7529857048368378</v>
+        <v>0.9017628173358933</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.6145969436164176</v>
+        <v>-0.3479486831568821</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6424428246706191</v>
+        <v>0.6447291239358884</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>070B</t>
+          <t>DR-199</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.6117988085944</v>
+        <v>1.117599235147628</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.3719363885370232</v>
+        <v>1.311542335946815</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9926850011759285</v>
+        <v>0.8947361066863296</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2889429052725138</v>
+        <v>0.009251491916314095</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.2451454947093375</v>
+        <v>-0.2920318550763781</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-200</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.001310616778274</v>
+        <v>-1.883207136766172</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.7970423066802681</v>
+        <v>-0.9457755438510638</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.8069020575122754</v>
+        <v>-0.7334271420827244</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.6693091208294252</v>
+        <v>-0.008832172010860211</v>
       </c>
       <c r="F54" t="n">
-        <v>1.327527915015708</v>
+        <v>1.520191052739634</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>072A</t>
+          <t>DR-201</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.196567122928959</v>
+        <v>1.365873452299084</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3816575243342818</v>
+        <v>0.4001821751317141</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.8780285286186853</v>
+        <v>-0.7329372239434282</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.4519796593601165</v>
+        <v>-0.3132921024594118</v>
       </c>
       <c r="F55" t="n">
-        <v>0.6040170954923145</v>
+        <v>0.7064176900369388</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.096900359822941</v>
+        <v>-0.9117356838546911</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.5034201415455477</v>
+        <v>-0.6444560362887453</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.765643611413162</v>
+        <v>-0.7215214466851259</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.1949253397929372</v>
+        <v>0.2509521206725095</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9048171608987922</v>
+        <v>0.9960670529704149</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>074B</t>
+          <t>DR-203</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.457357361954873</v>
+        <v>1.470275646889326</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6906888031549868</v>
+        <v>0.6932871059657355</v>
       </c>
       <c r="D57" t="n">
-        <v>0.8389259401030396</v>
+        <v>1.052179580057304</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.089164862209512</v>
+        <v>-0.8384178934652087</v>
       </c>
       <c r="F57" t="n">
-        <v>0.644149000566772</v>
+        <v>0.7438960006107376</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>075A</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.06931888684034995</v>
+        <v>-0.2665358785687708</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.6778851135954335</v>
+        <v>0.1970244488887461</v>
       </c>
       <c r="D58" t="n">
-        <v>0.05416675883708903</v>
+        <v>0.01404941742798321</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.007077329115208764</v>
+        <v>0.5017670299450843</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6974089372826383</v>
+        <v>0.6769301655565093</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>076ABC</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.565713443734886</v>
+        <v>1.406639132108725</v>
       </c>
       <c r="C59" t="n">
-        <v>0.5771976697224351</v>
+        <v>0.8807571543026934</v>
       </c>
       <c r="D59" t="n">
-        <v>1.518769705041111</v>
+        <v>1.737195949247308</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.02765254553193</v>
+        <v>-0.5931615424074456</v>
       </c>
       <c r="F59" t="n">
-        <v>1.03592345193109</v>
+        <v>1.064706823138831</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>077B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4958354836775877</v>
+        <v>-1.04654314824991</v>
       </c>
       <c r="C60" t="n">
-        <v>-1.276126690229168</v>
+        <v>0.3927026070129461</v>
       </c>
       <c r="D60" t="n">
-        <v>1.138800790845892</v>
+        <v>0.9696039345368295</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01635300782144605</v>
+        <v>0.7309184044148062</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4714097554142079</v>
+        <v>0.3864933548345862</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>078B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.248183987559397</v>
+        <v>1.322734165842922</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2293366422120424</v>
+        <v>0.5298493992195629</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8788726434704681</v>
+        <v>-0.7691381435656728</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.4222567098910349</v>
+        <v>-0.2590759509531653</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5300893791923758</v>
+        <v>0.6267737340491375</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>079C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-1.629344930425405</v>
+        <v>0.2883624340170752</v>
       </c>
       <c r="C62" t="n">
-        <v>-1.545965793606328</v>
+        <v>2.306563101200545</v>
       </c>
       <c r="D62" t="n">
-        <v>1.883657181569652</v>
+        <v>1.549604816270431</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.7171415380755964</v>
+        <v>-0.09682839531785646</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.7621412441534884</v>
+        <v>-0.7826836905049754</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>080C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.8143359583503489</v>
+        <v>-0.5999463788975359</v>
       </c>
       <c r="C63" t="n">
-        <v>-2.549339640250869</v>
+        <v>2.072153265991139</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3222800507219714</v>
+        <v>-0.280822161472688</v>
       </c>
       <c r="E63" t="n">
-        <v>0.09124438826377664</v>
+        <v>0.5866722147111101</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.662268624501678</v>
+        <v>-1.690308284118453</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>081B</t>
+          <t>DR-210</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.8666454775891798</v>
+        <v>3.259838203467713</v>
       </c>
       <c r="C64" t="n">
-        <v>4.11714272707234</v>
+        <v>-2.250912512067594</v>
       </c>
       <c r="D64" t="n">
-        <v>0.5992126459894362</v>
+        <v>1.354510712614848</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.249555986684579</v>
+        <v>-1.118769623188569</v>
       </c>
       <c r="F64" t="n">
-        <v>0.5188308775953528</v>
+        <v>0.5149997760813263</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>082A</t>
+          <t>DR-211</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.4664390218860258</v>
+        <v>1.28969354012254</v>
       </c>
       <c r="C65" t="n">
-        <v>1.163783490754887</v>
+        <v>-0.6357552595409152</v>
       </c>
       <c r="D65" t="n">
-        <v>1.678136740474815</v>
+        <v>1.704901386062717</v>
       </c>
       <c r="E65" t="n">
-        <v>0.4610386369034485</v>
+        <v>0.01399740642432244</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.418547744678785</v>
+        <v>-1.584159551385183</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>083B</t>
+          <t>DR-212</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2.559322661358479</v>
+        <v>-1.380782151697143</v>
       </c>
       <c r="C66" t="n">
-        <v>0.4614726896745833</v>
+        <v>-2.374660442649688</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3406514164978525</v>
+        <v>0.4170457761305625</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4923039941567495</v>
+        <v>0.4007192794125244</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.256439945046135</v>
+        <v>-0.2961970743657171</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>084A</t>
+          <t>DR-213</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.1833590236944858</v>
+        <v>0.8921544741120715</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7593348418801721</v>
+        <v>-0.5883266626024306</v>
       </c>
       <c r="D67" t="n">
-        <v>0.7600572844145105</v>
+        <v>0.7357202549034154</v>
       </c>
       <c r="E67" t="n">
-        <v>0.2824234538525312</v>
+        <v>-0.127091181504781</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.476889728309769</v>
+        <v>-1.540778182465563</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>085C</t>
+          <t>DR-214</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.2062927540824398</v>
+        <v>0.892595178371503</v>
       </c>
       <c r="C68" t="n">
-        <v>1.094883456612477</v>
+        <v>-1.209613023294545</v>
       </c>
       <c r="D68" t="n">
-        <v>0.310927032290314</v>
+        <v>0.3453260692163193</v>
       </c>
       <c r="E68" t="n">
-        <v>0.6135229963336868</v>
+        <v>0.06179160399207628</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.392886124822724</v>
+        <v>-1.47892212530216</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>086A</t>
+          <t>DR-215</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.2323062671952766</v>
+        <v>0.8955673300685464</v>
       </c>
       <c r="C69" t="n">
-        <v>1.142439652893049</v>
+        <v>-1.249781717392244</v>
       </c>
       <c r="D69" t="n">
-        <v>0.2671134776513809</v>
+        <v>0.3160314387682531</v>
       </c>
       <c r="E69" t="n">
-        <v>0.5643518615523497</v>
+        <v>0.006081752773845664</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.361693967845177</v>
+        <v>-1.435474450731464</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>088C</t>
+          <t>DR-216</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1.06604684963242</v>
+        <v>1.559479834969671</v>
       </c>
       <c r="C70" t="n">
-        <v>3.863599975206721</v>
+        <v>-3.500291563881063</v>
       </c>
       <c r="D70" t="n">
-        <v>1.538796007926314</v>
+        <v>2.364730317312989</v>
       </c>
       <c r="E70" t="n">
-        <v>0.3384122641324365</v>
+        <v>-0.1076943810406325</v>
       </c>
       <c r="F70" t="n">
-        <v>1.84037201739382</v>
+        <v>1.675585256092637</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>089A</t>
+          <t>DR-217</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.3343058201645225</v>
+        <v>1.239049323412609</v>
       </c>
       <c r="C71" t="n">
-        <v>1.346016920221777</v>
+        <v>-0.729840729151663</v>
       </c>
       <c r="D71" t="n">
-        <v>1.417310654024433</v>
+        <v>1.502761498249934</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.04980498403140576</v>
+        <v>-0.5474758874499401</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.464150418365424</v>
+        <v>-1.511129212506584</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>090B</t>
+          <t>DR-218</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.22414617859318</v>
+        <v>0.623945712484992</v>
       </c>
       <c r="C72" t="n">
-        <v>3.394002557863137</v>
+        <v>-4.211385529304803</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.347312507306263</v>
+        <v>0.4148352826728539</v>
       </c>
       <c r="E72" t="n">
-        <v>0.5969329919963716</v>
+        <v>0.08064999787314663</v>
       </c>
       <c r="F72" t="n">
-        <v>1.753550130458529</v>
+        <v>1.696369737002723</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>091C</t>
+          <t>DR-219</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.7226046072613844</v>
+        <v>1.567368716832424</v>
       </c>
       <c r="C73" t="n">
-        <v>1.91536032642679</v>
+        <v>-0.4797463537731478</v>
       </c>
       <c r="D73" t="n">
-        <v>1.960116775718661</v>
+        <v>2.287737583151497</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.24492248713509</v>
+        <v>-1.526473362587657</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.4625774809146626</v>
+        <v>-0.3553800098316978</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>092ABC</t>
+          <t>DR-220</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.009030700152493264</v>
+        <v>0.7627497771168492</v>
       </c>
       <c r="C74" t="n">
-        <v>0.663321269840135</v>
+        <v>-0.7288271942523658</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1114350703918355</v>
+        <v>0.1074828587996874</v>
       </c>
       <c r="E74" t="n">
-        <v>0.3789455712302828</v>
+        <v>0.0201831942738715</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.131050796970574</v>
+        <v>-1.174374700424869</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>093C</t>
+          <t>DR-221</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.3763606133978886</v>
+        <v>2.187162644397314</v>
       </c>
       <c r="C75" t="n">
-        <v>2.817122048074689</v>
+        <v>-1.869328212064634</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.7012297058721044</v>
+        <v>-0.04978826043656984</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.1420613312442256</v>
+        <v>-0.4797864609368293</v>
       </c>
       <c r="F75" t="n">
-        <v>1.617291290610245</v>
+        <v>1.657534513145848</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-222</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1.417328230036715</v>
+        <v>1.360712257745901</v>
       </c>
       <c r="C76" t="n">
-        <v>3.554954813771848</v>
+        <v>-3.636827221020447</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.183383788576439</v>
+        <v>-0.4587251497869458</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.09691839241902159</v>
+        <v>-0.9317114291446074</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7133465701814387</v>
+        <v>0.8502036983973567</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>095A</t>
+          <t>DR-223</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.1689377811729647</v>
+        <v>0.8213683318456481</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3831356444450521</v>
+        <v>-0.5404902516714791</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.4685531005305365</v>
+        <v>-0.5448040962418338</v>
       </c>
       <c r="E77" t="n">
-        <v>0.60032951261731</v>
+        <v>0.2172649608860132</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.303741372396725</v>
+        <v>-1.350350655482779</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>096A</t>
+          <t>DR-224</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.3590012634847855</v>
+        <v>1.113141778360852</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8035154282327985</v>
+        <v>-0.6046252807475098</v>
       </c>
       <c r="D78" t="n">
-        <v>0.6718265569508393</v>
+        <v>0.6523262358003026</v>
       </c>
       <c r="E78" t="n">
-        <v>0.6390465394387121</v>
+        <v>0.2322924966249524</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.284366653031746</v>
+        <v>-1.418128322759286</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>097ABC</t>
+          <t>DR-225</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.7189652708238128</v>
+        <v>3.147623705874303</v>
       </c>
       <c r="C79" t="n">
-        <v>4.168871634804006</v>
+        <v>-2.328259187295709</v>
       </c>
       <c r="D79" t="n">
-        <v>0.6784819261644851</v>
+        <v>1.438098103721796</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.4321596867230139</v>
+        <v>-1.339315730175941</v>
       </c>
       <c r="F79" t="n">
-        <v>0.3507633909833382</v>
+        <v>0.3840768903960989</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>098C</t>
+          <t>DR-226</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4798310722172192</v>
+        <v>0.2212994062533301</v>
       </c>
       <c r="C80" t="n">
-        <v>0.3872381000677153</v>
+        <v>-1.018850736989154</v>
       </c>
       <c r="D80" t="n">
-        <v>0.9798212151336515</v>
+        <v>0.9606504871898858</v>
       </c>
       <c r="E80" t="n">
-        <v>1.129941558164552</v>
+        <v>1.059493705688451</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.3532211163818461</v>
+        <v>-0.6052000335452624</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>099C</t>
+          <t>DR-227</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.3199341128251685</v>
+        <v>1.2618957285508</v>
       </c>
       <c r="C81" t="n">
-        <v>1.422366666820033</v>
+        <v>-0.7798011662148846</v>
       </c>
       <c r="D81" t="n">
-        <v>0.8766065495481625</v>
+        <v>1.039902858136471</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.2755521885562139</v>
+        <v>-0.700490209926519</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.9612705689132806</v>
+        <v>-0.9418430116527419</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>DR-228</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.0718581053026633</v>
+        <v>0.7404018156687671</v>
       </c>
       <c r="C82" t="n">
-        <v>0.6735217188513775</v>
+        <v>-0.8299742191834467</v>
       </c>
       <c r="D82" t="n">
-        <v>0.1578429358406298</v>
+        <v>0.1301954230624895</v>
       </c>
       <c r="E82" t="n">
-        <v>0.5418148634999916</v>
+        <v>0.1248325411554945</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.320018729159598</v>
+        <v>-1.389925865269606</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>101C</t>
+          <t>DR-229</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-1.247032889555265</v>
+        <v>2.0120687216128</v>
       </c>
       <c r="C83" t="n">
-        <v>1.751725829155909</v>
+        <v>-0.2180522860343177</v>
       </c>
       <c r="D83" t="n">
-        <v>1.70630441391975</v>
+        <v>1.96490923575631</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.5685760761162181</v>
+        <v>-0.8673500453384335</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.4576243986313975</v>
+        <v>-0.47388347725678</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>102B</t>
+          <t>DR-230</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.3505986527251582</v>
+        <v>0.5915015307025024</v>
       </c>
       <c r="C84" t="n">
-        <v>0.8974259404505437</v>
+        <v>-1.014216750802971</v>
       </c>
       <c r="D84" t="n">
-        <v>-1.174413971607768</v>
+        <v>-1.04023999023398</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.4629362394335262</v>
+        <v>-0.8489873222854308</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.7619128057751003</v>
+        <v>-0.5603201598500775</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>103A</t>
+          <t>DR-231</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.03491153023906608</v>
+        <v>0.8884212964535518</v>
       </c>
       <c r="C85" t="n">
-        <v>0.7926783593169394</v>
+        <v>-0.9191389082035453</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.4127303700398317</v>
+        <v>-0.4114423901415541</v>
       </c>
       <c r="E85" t="n">
-        <v>0.4912344157236574</v>
+        <v>-0.003275781965141877</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.314080933109209</v>
+        <v>-1.336408425371881</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>104C</t>
+          <t>DR-232</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.725980439622903</v>
+        <v>-0.7636526843932201</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.7934045896191158</v>
+        <v>-0.2183387449209146</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.01619457357408428</v>
+        <v>-0.1458031811706514</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1529730180855387</v>
+        <v>0.4811366446048787</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.07905835095790237</v>
+        <v>-0.08872060028805895</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>105C</t>
+          <t>DR-233</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.946704198945496</v>
+        <v>0.5608002450283576</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.6215209409844631</v>
+        <v>0.8938361178504501</v>
       </c>
       <c r="D87" t="n">
-        <v>1.200509910889856</v>
+        <v>0.9874342496512107</v>
       </c>
       <c r="E87" t="n">
-        <v>0.2639825191520685</v>
+        <v>0.470607252785713</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.7995439896508373</v>
+        <v>-0.9341802355491712</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>106B</t>
+          <t>DR-234</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.9989848786498587</v>
+        <v>0.926360750822938</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.3340269928241231</v>
+        <v>0.4970458386682418</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2238203608891341</v>
+        <v>0.1079824782198825</v>
       </c>
       <c r="E88" t="n">
-        <v>0.8116594153644122</v>
+        <v>0.9915083333912991</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.07623528027315138</v>
+        <v>-0.265848786409599</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>107C</t>
+          <t>DR-235</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-1.215905235012254</v>
+        <v>0.843776633246935</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.439481415147648</v>
+        <v>0.9873124469458763</v>
       </c>
       <c r="D89" t="n">
-        <v>1.138312703977657</v>
+        <v>0.9868463822322535</v>
       </c>
       <c r="E89" t="n">
-        <v>0.1230578701987501</v>
+        <v>0.3540789276325437</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.5136322714365706</v>
+        <v>-0.6308753927717167</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>108B</t>
+          <t>DR-11</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-1.417173286113156</v>
+        <v>0.9719330876083827</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.1915950646896195</v>
+        <v>1.172660593963664</v>
       </c>
       <c r="D90" t="n">
-        <v>1.424837756460075</v>
+        <v>1.392421305002357</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.581824824772323</v>
+        <v>-0.22586803890006</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.02494958570959774</v>
+        <v>-0.04612867903110496</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-12</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.1719008394752966</v>
+        <v>-0.2220736943655576</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.7383546539828668</v>
+        <v>0.09106705837697232</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.56047937599453</v>
+        <v>-0.7401107171666392</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1280332251186704</v>
+        <v>0.2482363779060724</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.6935690835140843</v>
+        <v>-0.659332190830568</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">111C </t>
+          <t>DR-13</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.6857861504012766</v>
+        <v>-1.313419316705872</v>
       </c>
       <c r="C92" t="n">
-        <v>-1.148847834136137</v>
+        <v>0.08320432295893813</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.03817262654399298</v>
+        <v>-0.4083796171089709</v>
       </c>
       <c r="E92" t="n">
-        <v>0.3909009068335315</v>
+        <v>-0.04560534853192665</v>
       </c>
       <c r="F92" t="n">
-        <v>-1.106608827982852</v>
+        <v>-0.2191190809626833</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>113B</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.9280774242422849</v>
+        <v>0.2038854870689811</v>
       </c>
       <c r="C93" t="n">
-        <v>-1.71865682567192</v>
+        <v>0.92983749005909</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.2141180843017445</v>
+        <v>-0.3597666969711319</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.06219201091441032</v>
+        <v>0.5605794238895954</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.8676091720056124</v>
+        <v>-1.169754513918243</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>114B</t>
+          <t>DR-16</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6510316082800551</v>
+        <v>-1.451723592198524</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.492949561234742</v>
+        <v>0.3111631246599663</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2901862772196361</v>
+        <v>-0.5590549792489959</v>
       </c>
       <c r="E94" t="n">
-        <v>0.1594064755723946</v>
+        <v>0.3393075141378818</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.6380041344501566</v>
+        <v>-0.8032634385167114</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>115ABC</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-1.150985881579185</v>
+        <v>-1.127456530866633</v>
       </c>
       <c r="C95" t="n">
-        <v>0.2259774506146397</v>
+        <v>0.3302977125587144</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.2521830143437926</v>
+        <v>-0.01607167907238776</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.2462504007773956</v>
+        <v>0.5800974001296716</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.1302013965031049</v>
+        <v>-0.6607864244891269</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>116B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5913657838179265</v>
+        <v>1.249769074429006</v>
       </c>
       <c r="C96" t="n">
-        <v>-1.206424894499996</v>
+        <v>0.477045291532891</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.6802555747294913</v>
+        <v>-0.2190023438501779</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.3838880633339555</v>
+        <v>-0.2061161611631226</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.9450023063477527</v>
+        <v>-0.08913345463964165</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>117ABC</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.937394931562584</v>
+        <v>-0.8887951985271337</v>
       </c>
       <c r="C97" t="n">
-        <v>-1.096161650843436</v>
+        <v>0.2488909975114484</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.2042511578618776</v>
+        <v>-0.9284453999553191</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.4633249089873731</v>
+        <v>-0.164975273769095</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.5817225588894583</v>
+        <v>-0.7925574029886051</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>118A</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.9522750529103752</v>
+        <v>-1.168438879038866</v>
       </c>
       <c r="C98" t="n">
-        <v>-1.080260607146061</v>
+        <v>-0.003130631984780151</v>
       </c>
       <c r="D98" t="n">
-        <v>0.4705917137332317</v>
+        <v>-0.3947826144622123</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.658239267589489</v>
+        <v>-0.1436342549739596</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.3831352722200428</v>
+        <v>-0.4467765633914335</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>119B</t>
+          <t>DR-22</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.4712149774326275</v>
+        <v>-1.281579028358656</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.9031947143233104</v>
+        <v>0.08514905381541617</v>
       </c>
       <c r="D99" t="n">
-        <v>0.2728592816484948</v>
+        <v>0.3048592097081259</v>
       </c>
       <c r="E99" t="n">
-        <v>0.5551535494782703</v>
+        <v>-0.2232731962541838</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.9841459484117515</v>
+        <v>-0.2620362327777286</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1.127484605899417</v>
+        <v>0.1781115976906532</v>
       </c>
       <c r="C100" t="n">
-        <v>-1.406890591928486</v>
+        <v>0.5988880130079813</v>
       </c>
       <c r="D100" t="n">
-        <v>0.5542638000294198</v>
+        <v>-0.003701104498106644</v>
       </c>
       <c r="E100" t="n">
-        <v>0.09048492506852537</v>
+        <v>0.695853619065426</v>
       </c>
       <c r="F100" t="n">
-        <v>-1.976987683739476</v>
+        <v>-1.095461284324403</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-24</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5920456535947561</v>
+        <v>-1.406676358879901</v>
       </c>
       <c r="C101" t="n">
-        <v>0.6012894216807224</v>
+        <v>0.0005335560651409531</v>
       </c>
       <c r="D101" t="n">
-        <v>-1.183884765454769</v>
+        <v>0.1460756073066123</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.2096775406117627</v>
+        <v>0.1784112205141717</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.113102190614182</v>
+        <v>-1.957446719124258</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>123A</t>
+          <t>DR-25</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.03807955786515318</v>
+        <v>0.2908944714649704</v>
       </c>
       <c r="C102" t="n">
-        <v>0.548434532165184</v>
+        <v>-1.048708972583472</v>
       </c>
       <c r="D102" t="n">
-        <v>2.240039292070825</v>
+        <v>-1.142566476999774</v>
       </c>
       <c r="E102" t="n">
-        <v>0.1832179568225979</v>
+        <v>-0.6168100122163176</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.4507124298135309</v>
+        <v>-0.944696292838468</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>124A</t>
+          <t>DR-26</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-0.1611338745056887</v>
+        <v>0.3751096272332076</v>
       </c>
       <c r="C103" t="n">
-        <v>1.139332570103232</v>
+        <v>-0.4556479342905045</v>
       </c>
       <c r="D103" t="n">
-        <v>1.741794068591849</v>
+        <v>2.269027853107756</v>
       </c>
       <c r="E103" t="n">
-        <v>0.3411648699546696</v>
+        <v>0.2194051449306801</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.2156500958295954</v>
+        <v>-0.6183897980064643</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-27</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1.572954036003847</v>
+        <v>0.9485634729796942</v>
       </c>
       <c r="C104" t="n">
-        <v>0.661961363680561</v>
+        <v>-0.802044310294847</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.2043248632962611</v>
+        <v>1.887461237689857</v>
       </c>
       <c r="E104" t="n">
-        <v>0.7089713321305537</v>
+        <v>0.2105495138271185</v>
       </c>
       <c r="F104" t="n">
-        <v>0.1104196070970546</v>
+        <v>-0.3870012202386428</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>126A</t>
+          <t>DR-28</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-0.8825951739504888</v>
+        <v>-0.4313313670775923</v>
       </c>
       <c r="C105" t="n">
-        <v>1.238620674692621</v>
+        <v>-1.941893637056142</v>
       </c>
       <c r="D105" t="n">
-        <v>0.1785510530204289</v>
+        <v>-0.08100710000537174</v>
       </c>
       <c r="E105" t="n">
-        <v>0.621601581492661</v>
+        <v>0.595277119053314</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.1296247493155299</v>
+        <v>0.03388224377310044</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>127B</t>
+          <t>DR-29</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.03144369392340967</v>
+        <v>1.761067850713715</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.2071600440574938</v>
+        <v>-0.5849038701386391</v>
       </c>
       <c r="D106" t="n">
-        <v>0.5326934333387001</v>
+        <v>0.3390608660981065</v>
       </c>
       <c r="E106" t="n">
-        <v>0.4837709560684983</v>
+        <v>0.3367113843004378</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.8341149890039792</v>
+        <v>-0.2675423190331854</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>128B</t>
+          <t>DR-30</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-0.7663165359156948</v>
+        <v>0.1662737388245466</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.09875611758934576</v>
+        <v>-0.1705463668408114</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.6137700815252349</v>
+        <v>0.398380357261954</v>
       </c>
       <c r="E107" t="n">
-        <v>0.02741275919977134</v>
+        <v>0.4809767387878069</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.4616488495588811</v>
+        <v>-0.937086977672977</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>129A</t>
+          <t>DR-31</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.3411344821124125</v>
+        <v>0.8594419372146931</v>
       </c>
       <c r="C108" t="n">
-        <v>0.3041607408931654</v>
+        <v>0.3276494381253601</v>
       </c>
       <c r="D108" t="n">
-        <v>-1.150382567365621</v>
+        <v>-0.6715962415919978</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.412826520865124</v>
+        <v>0.02752228359918108</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.1881695958883191</v>
+        <v>-0.4308992524878855</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>130A</t>
+          <t>DR-33</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-1.137861568920309</v>
+        <v>0.2157919675251186</v>
       </c>
       <c r="C109" t="n">
-        <v>1.012376191670969</v>
+        <v>-0.6285139929803554</v>
       </c>
       <c r="D109" t="n">
-        <v>0.488922342976493</v>
+        <v>-1.06706147390188</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.2250024565718885</v>
+        <v>-0.4847407741226794</v>
       </c>
       <c r="F109" t="n">
-        <v>0.2332591035556069</v>
+        <v>-0.01607621163064961</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>131B</t>
+          <t>DR-34</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-0.9481149886558807</v>
+        <v>-2.356049912301366</v>
       </c>
       <c r="C110" t="n">
-        <v>1.110543628009871</v>
+        <v>-1.000619044880821</v>
       </c>
       <c r="D110" t="n">
-        <v>0.9329284959000244</v>
+        <v>-0.1141134140618024</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.1512499960494758</v>
+        <v>-0.5734459806097036</v>
       </c>
       <c r="F110" t="n">
-        <v>0.4433743761182506</v>
+        <v>0.5892179178110307</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>132B</t>
+          <t>DR-35</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5204242725805359</v>
+        <v>1.624608965022578</v>
       </c>
       <c r="C111" t="n">
-        <v>0.8980639533605057</v>
+        <v>-0.003580861411544615</v>
       </c>
       <c r="D111" t="n">
-        <v>-1.278063622507802</v>
+        <v>0.6819820050301705</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.2736809595080166</v>
+        <v>-0.2645338642146947</v>
       </c>
       <c r="F111" t="n">
-        <v>-1.09915585554474</v>
+        <v>0.2155655937275834</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-36</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-0.5836465725462537</v>
+        <v>1.49536190043393</v>
       </c>
       <c r="C112" t="n">
-        <v>1.008837671910651</v>
+        <v>-0.183638209870917</v>
       </c>
       <c r="D112" t="n">
-        <v>-1.405062382453081</v>
+        <v>1.156985584069798</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.5605856024177192</v>
+        <v>-0.1369499196172169</v>
       </c>
       <c r="F112" t="n">
-        <v>0.7317835885661054</v>
+        <v>0.3817212110485114</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>134C</t>
+          <t>DR-37</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-0.03157379610505155</v>
+        <v>0.5226168831775103</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.6224287511638756</v>
+        <v>-1.188548765298282</v>
       </c>
       <c r="D113" t="n">
-        <v>-1.337092709965395</v>
+        <v>-1.18148501166844</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.5417735081220331</v>
+        <v>-0.7670403416825</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.6233791384455339</v>
+        <v>-0.912914050681513</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>135A</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-0.8396837594067276</v>
+        <v>1.300935726559798</v>
       </c>
       <c r="C114" t="n">
-        <v>0.9558557536453666</v>
+        <v>-0.4555396020020679</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.04568079737625368</v>
+        <v>-1.119663270002206</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.3691249064053957</v>
+        <v>-0.6151173626827413</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.2408229922447522</v>
+        <v>0.9055766399470755</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>136B</t>
+          <t>DR-39</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-1.215931307913357</v>
+        <v>-0.03744776669413047</v>
       </c>
       <c r="C115" t="n">
-        <v>0.6462842368046466</v>
+        <v>0.269835437933464</v>
       </c>
       <c r="D115" t="n">
-        <v>-1.103391793964134</v>
+        <v>-1.450219547001383</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.9394669561266468</v>
+        <v>-0.4535269529633088</v>
       </c>
       <c r="F115" t="n">
-        <v>0.9757331154920781</v>
+        <v>-0.4177276251385384</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>137A</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-1.747021847959936</v>
+        <v>1.415799277302479</v>
       </c>
       <c r="C116" t="n">
-        <v>0.05564665797353333</v>
+        <v>-0.1717301514345537</v>
       </c>
       <c r="D116" t="n">
-        <v>-1.982667331554445</v>
+        <v>0.1113413495962662</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.4680479177636737</v>
+        <v>-0.5461881682106717</v>
       </c>
       <c r="F116" t="n">
-        <v>1.564018973504618</v>
+        <v>-0.1759821692860163</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>138B</t>
+          <t>DR-41</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-0.8136753824243101</v>
+        <v>1.459088147441155</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.4837160504351651</v>
+        <v>0.3474812302192355</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.2857074706965364</v>
+        <v>-0.8505380258777518</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.005621908735641195</v>
+        <v>-0.7698823252774922</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0526190805216716</v>
+        <v>1.175808437840083</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-42</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-0.5950710508977713</v>
+        <v>1.646597870879473</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.005568627319767915</v>
+        <v>0.8962849264454397</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.8515268705891459</v>
+        <v>-1.800104642054339</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.3394538605693931</v>
+        <v>-0.08411472314449017</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.1329844644758153</v>
+        <v>1.703435424171945</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>140C</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-0.4182065684671912</v>
+        <v>0.5972647618262127</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.1481342522466468</v>
+        <v>0.6494442114146532</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.6205621945718354</v>
+        <v>-0.3637082149673459</v>
       </c>
       <c r="E119" t="n">
-        <v>0.3280784319306864</v>
+        <v>0.264805547713395</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.1318988679585089</v>
+        <v>0.05065119426018467</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>141B</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-0.5634214294000531</v>
+        <v>0.7271643412531225</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.3840260093169507</v>
+        <v>0.2251225986889984</v>
       </c>
       <c r="D120" t="n">
-        <v>0.3897717727285006</v>
+        <v>-0.8380958319135163</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.3479308110126207</v>
+        <v>-0.2800959193650074</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.05578950961641631</v>
+        <v>-0.02135145820869932</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>142C</t>
+          <t>DR-46</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-0.9372917639956571</v>
+        <v>-1.932716045143131</v>
       </c>
       <c r="C121" t="n">
-        <v>0.4408483496164899</v>
+        <v>-0.1448172930791965</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.2322712539692014</v>
+        <v>-0.5448038560177437</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.1854636368553419</v>
+        <v>-0.1419617867396689</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.1920719412164539</v>
+        <v>0.3958184822911778</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>143B</t>
+          <t>DR-47</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-0.2742046900319732</v>
+        <v>0.5968930820592315</v>
       </c>
       <c r="C122" t="n">
-        <v>0.1433801608794345</v>
+        <v>0.03578056088284124</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.5392153140194204</v>
+        <v>-0.6661649821300104</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1655892475499653</v>
+        <v>0.3992511284488507</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.2454376670455168</v>
+        <v>-0.1570761522220875</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>144B</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-0.1337164747089373</v>
+        <v>0.3453546125983817</v>
       </c>
       <c r="C123" t="n">
-        <v>0.2202091990460062</v>
+        <v>0.5638137204620016</v>
       </c>
       <c r="D123" t="n">
-        <v>0.2161202504399982</v>
+        <v>0.3337532190942668</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.1327026937840058</v>
+        <v>-0.05375335551118025</v>
       </c>
       <c r="F123" t="n">
-        <v>0.1474645225806289</v>
+        <v>-0.02974210731796725</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>145B</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.1100906591718397</v>
+        <v>1.227276573991194</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1707902440610926</v>
+        <v>0.172585937610626</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.55597193001903</v>
+        <v>-0.1680930939307997</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.711624788567324</v>
+        <v>-0.2278996511076564</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.2001093786499658</v>
+        <v>-0.1555600979302187</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>146B</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-0.7179928884722595</v>
+        <v>0.6325241962086973</v>
       </c>
       <c r="C125" t="n">
-        <v>0.5220453606967514</v>
+        <v>-0.2051487394024441</v>
       </c>
       <c r="D125" t="n">
-        <v>0.9702758191188696</v>
+        <v>-0.5355316664281644</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.8201389479262819</v>
+        <v>0.1408242769075625</v>
       </c>
       <c r="F125" t="n">
-        <v>0.06155511687173418</v>
+        <v>-0.2375412593642658</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>147A</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>-2.679269731680175</v>
+        <v>0.4234958850744875</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.3801395712714734</v>
+        <v>-0.2103573135118748</v>
       </c>
       <c r="D126" t="n">
-        <v>3.210953068685853</v>
+        <v>0.2798382035671283</v>
       </c>
       <c r="E126" t="n">
-        <v>-1.934304350057394</v>
+        <v>0.001338646340691127</v>
       </c>
       <c r="F126" t="n">
-        <v>0.4525126622058024</v>
+        <v>0.1538217109531625</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>148B</t>
+          <t>DR-52</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.2765155769125489</v>
+        <v>0.2028575044055422</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.4243983658556779</v>
+        <v>-0.2482280534536234</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.7631485353763863</v>
+        <v>-0.4907234616749766</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.5269466269596144</v>
+        <v>-0.6740149144439633</v>
       </c>
       <c r="F127" t="n">
-        <v>0.00787241217101816</v>
+        <v>-0.01850241156073975</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>149C</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-1.398017493668135</v>
+        <v>0.8657592407708553</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.1542487181058697</v>
+        <v>0.2421777573343523</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.2710499281125677</v>
+        <v>1.096574722981461</v>
       </c>
       <c r="E128" t="n">
-        <v>0.1724081893654863</v>
+        <v>-0.6780896968316789</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.08850492293296366</v>
+        <v>0.1348388209240637</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>150B</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-0.5120266057745779</v>
+        <v>1.391099997691936</v>
       </c>
       <c r="C129" t="n">
-        <v>0.2592203008263455</v>
+        <v>2.682546342659008</v>
       </c>
       <c r="D129" t="n">
-        <v>1.000461923776302</v>
+        <v>3.223351784624087</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.3498830232930421</v>
+        <v>-1.147235698623695</v>
       </c>
       <c r="F129" t="n">
-        <v>0.2192988091821678</v>
+        <v>0.5185483136051035</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-0.8308891455401692</v>
+        <v>-0.2430877776098537</v>
       </c>
       <c r="C130" t="n">
-        <v>0.7359552014480247</v>
+        <v>-0.0349127371516423</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.03605039658895762</v>
+        <v>-0.7851459780554861</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.04020243597102634</v>
+        <v>-0.2956382938542433</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.0389230310083802</v>
+        <v>0.1643484658312315</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>DR-57</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-0.7270424334232468</v>
+        <v>1.28129006283607</v>
       </c>
       <c r="C131" t="n">
-        <v>0.6446437800704674</v>
+        <v>0.7836645218295752</v>
       </c>
       <c r="D131" t="n">
-        <v>0.1303509406343024</v>
+        <v>-0.3248686008585621</v>
       </c>
       <c r="E131" t="n">
-        <v>0.3439730126956387</v>
+        <v>0.3041861703627555</v>
       </c>
       <c r="F131" t="n">
-        <v>0.1433288122186912</v>
+        <v>-0.1338230400840711</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>DR-58</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-0.5168849408402334</v>
+        <v>-1.456933782449376</v>
       </c>
       <c r="C132" t="n">
-        <v>0.9254191415288148</v>
+        <v>0.09970184761178014</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.442034631827324</v>
+        <v>-0.7509468439072748</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.2666492231191814</v>
+        <v>-0.1067104124138202</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.40325581175349</v>
+        <v>-0.760760699584229</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-0.9965114403039921</v>
+        <v>0.6181977721414004</v>
       </c>
       <c r="C133" t="n">
-        <v>2.191641329357376</v>
+        <v>0.1487039033518334</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.8989852647138913</v>
+        <v>1.074770444724477</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.6114922044864066</v>
+        <v>-0.1248915430436371</v>
       </c>
       <c r="F133" t="n">
-        <v>0.591283363961861</v>
+        <v>0.2021868480815069</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>DR-60</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-0.7810323591180083</v>
+        <v>-1.457306175652346</v>
       </c>
       <c r="C134" t="n">
-        <v>0.5973149737362101</v>
+        <v>1.513184437525751</v>
       </c>
       <c r="D134" t="n">
-        <v>0.5918076415729455</v>
+        <v>2.218026213289593</v>
       </c>
       <c r="E134" t="n">
-        <v>-1.322375014701732</v>
+        <v>-1.282275628680417</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.4429276944454076</v>
+        <v>0.05540215613279888</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>DR-61</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>2.08981008359123</v>
+        <v>0.7803276027461462</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.6643786936165206</v>
+        <v>0.4907914406787362</v>
       </c>
       <c r="D135" t="n">
-        <v>-1.545837545687278</v>
+        <v>0.843427986102082</v>
       </c>
       <c r="E135" t="n">
-        <v>-1.898548484890369</v>
+        <v>0.5386126973286453</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.2451414007491668</v>
+        <v>-0.6274872491043106</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>DR-62</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-0.8383674869864858</v>
+        <v>-1.990845631690254</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.9813582419938359</v>
+        <v>0.2355604898973365</v>
       </c>
       <c r="D136" t="n">
-        <v>0.3175234855117375</v>
+        <v>0.6081807056095</v>
       </c>
       <c r="E136" t="n">
-        <v>0.5032309827180014</v>
+        <v>-0.4717110261472354</v>
       </c>
       <c r="F136" t="n">
-        <v>0.7573681179936876</v>
+        <v>-0.1110918340120499</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>DR-63</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.1098385008120663</v>
+        <v>-4.656189542291576</v>
       </c>
       <c r="C137" t="n">
-        <v>0.9958364680804005</v>
+        <v>1.643650117285028</v>
       </c>
       <c r="D137" t="n">
-        <v>0.8778877468644745</v>
+        <v>-0.02345038062790589</v>
       </c>
       <c r="E137" t="n">
-        <v>0.9968351990478954</v>
+        <v>0.9142940336914476</v>
       </c>
       <c r="F137" t="n">
-        <v>0.217749031005661</v>
+        <v>-0.3548467003737049</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>DR-64</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-1.087925275322582</v>
+        <v>-1.219775451498179</v>
       </c>
       <c r="C138" t="n">
-        <v>0.09226818112593939</v>
+        <v>0.6486738267199559</v>
       </c>
       <c r="D138" t="n">
-        <v>0.5488054842193888</v>
+        <v>0.8699571133479909</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.4114491240058832</v>
+        <v>-1.887522891308214</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.1862915292055592</v>
+        <v>-0.3808581565055428</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>DR-66</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-0.6246046587468299</v>
+        <v>-0.5569712276307415</v>
       </c>
       <c r="C139" t="n">
-        <v>0.28377321205117</v>
+        <v>0.8522832794290223</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.7698784722254348</v>
+        <v>1.322641448538599</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.0516511659884679</v>
+        <v>0.1133817576139991</v>
       </c>
       <c r="F139" t="n">
-        <v>0.4443810337713628</v>
+        <v>-0.9791397177475313</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>DBC2</t>
+          <t>DR-67</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-0.8458566616939242</v>
+        <v>-1.331596706465817</v>
       </c>
       <c r="C140" t="n">
-        <v>-1.787994893473264</v>
+        <v>1.145079191033204</v>
       </c>
       <c r="D140" t="n">
-        <v>0.3786049263063122</v>
+        <v>0.2151263703683503</v>
       </c>
       <c r="E140" t="n">
-        <v>0.5838739956840345</v>
+        <v>-0.4937248500318229</v>
       </c>
       <c r="F140" t="n">
-        <v>0.1402525708920665</v>
+        <v>-0.38134678146129</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>DCC2</t>
+          <t>DR-68</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-2.389935285382684</v>
+        <v>-0.4506294434492785</v>
       </c>
       <c r="C141" t="n">
-        <v>-1.654303106010614</v>
+        <v>1.054331872074316</v>
       </c>
       <c r="D141" t="n">
-        <v>0.7076972505932342</v>
+        <v>1.761307898683762</v>
       </c>
       <c r="E141" t="n">
-        <v>-1.637997916260876</v>
+        <v>0.5477619699686903</v>
       </c>
       <c r="F141" t="n">
-        <v>1.044117156902698</v>
+        <v>0.7268721748116924</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>DCE3</t>
+          <t>DR-69</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-1.089589851598733</v>
+        <v>-3.116407163984135</v>
       </c>
       <c r="C142" t="n">
-        <v>-1.823190719549018</v>
+        <v>2.300084669204082</v>
       </c>
       <c r="D142" t="n">
-        <v>1.167867333375892</v>
+        <v>1.616432392182333</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.3302170889899362</v>
+        <v>0.09782539886532697</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.1399968759411037</v>
+        <v>-1.309808534925391</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>DJC2</t>
+          <t>DR-70</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.1756716270923005</v>
+        <v>-2.982598981983696</v>
       </c>
       <c r="C143" t="n">
-        <v>-2.152861821662257</v>
+        <v>-0.168336649913925</v>
       </c>
       <c r="D143" t="n">
-        <v>0.7391308236133235</v>
+        <v>1.014865593294066</v>
       </c>
       <c r="E143" t="n">
-        <v>1.227550219817453</v>
+        <v>-0.7752242776667423</v>
       </c>
       <c r="F143" t="n">
-        <v>1.16977939483472</v>
+        <v>0.4649077191125631</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-71</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-2.074578709120436</v>
+        <v>-0.5086817211014245</v>
       </c>
       <c r="C144" t="n">
-        <v>-2.408806640168555</v>
+        <v>-0.7432074948582049</v>
       </c>
       <c r="D144" t="n">
-        <v>-1.199017299351756</v>
+        <v>-0.7318087484845118</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.4233585444245123</v>
+        <v>-0.1959209183944553</v>
       </c>
       <c r="F144" t="n">
-        <v>0.5658699012725561</v>
+        <v>0.7396205359618376</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>MCE2</t>
+          <t>DR-72</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-1.098343697747283</v>
+        <v>-0.6097209923634681</v>
       </c>
       <c r="C145" t="n">
-        <v>-1.558812769315629</v>
+        <v>0.8328341733851955</v>
       </c>
       <c r="D145" t="n">
-        <v>0.7258464799987073</v>
+        <v>1.707415099011681</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.0851618034058515</v>
+        <v>0.4327133671303845</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.1114944708683335</v>
+        <v>1.178303452170473</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-73</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-0.139485385356923</v>
+        <v>-0.09838152828851204</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.1080131028737924</v>
+        <v>0.07504044247652165</v>
       </c>
       <c r="D146" t="n">
-        <v>-1.009464121093142</v>
+        <v>0.8873839204259811</v>
       </c>
       <c r="E146" t="n">
-        <v>0.4467713297472463</v>
+        <v>-1.087240734509707</v>
       </c>
       <c r="F146" t="n">
-        <v>0.634948694137763</v>
+        <v>0.02350819232795808</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-74</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-0.5742330100296753</v>
+        <v>-0.6447036771768387</v>
       </c>
       <c r="C147" t="n">
-        <v>0.5439964092491547</v>
+        <v>1.482246783549205</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.9036820810859044</v>
+        <v>0.9431943837783184</v>
       </c>
       <c r="E147" t="n">
-        <v>0.2879296034855099</v>
+        <v>-1.007587860612059</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.239055174562098</v>
+        <v>0.03481489210896636</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>DR-75</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-0.3456189527205129</v>
+        <v>-1.456988275136608</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.04228982195396233</v>
+        <v>2.014040071940022</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.2561179641815038</v>
+        <v>0.9733288268368592</v>
       </c>
       <c r="E148" t="n">
-        <v>0.2480716514951733</v>
+        <v>-0.5560638051034165</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.2973924354387451</v>
+        <v>0.8511794022984105</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>DR-77</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.8201540273188695</v>
+        <v>-0.8420463444754435</v>
       </c>
       <c r="C149" t="n">
-        <v>0.1828066116806836</v>
+        <v>1.616552839967399</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.1426256935533275</v>
+        <v>0.748917032521021</v>
       </c>
       <c r="E149" t="n">
-        <v>0.46256796671379</v>
+        <v>-1.270568450504729</v>
       </c>
       <c r="F149" t="n">
-        <v>0.4268889745418138</v>
+        <v>0.2806874274625368</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>DR-78</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1.405448406403489</v>
+        <v>-0.4275782826860983</v>
       </c>
       <c r="C150" t="n">
-        <v>0.4621943747491156</v>
+        <v>2.258063331542969</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.811918472391857</v>
+        <v>-0.8064082105777101</v>
       </c>
       <c r="E150" t="n">
-        <v>-1.993204597183884</v>
+        <v>-0.3183263683688481</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.7730532360583282</v>
+        <v>-0.01531898117523263</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>DR-79</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-0.6063654286120281</v>
+        <v>0.5195643385964016</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.4831523212811525</v>
+        <v>1.362575976464149</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.6937562931166502</v>
+        <v>0.5465492297189518</v>
       </c>
       <c r="E151" t="n">
-        <v>0.3259666145118036</v>
+        <v>0.1779333940630678</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.5939741470090641</v>
+        <v>0.3965701492875865</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>DR-80</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1.969248832367311</v>
+        <v>-0.6765974967521401</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.630176650832323</v>
+        <v>0.6111145076232468</v>
       </c>
       <c r="D152" t="n">
-        <v>-1.258011471069793</v>
+        <v>1.075009514910722</v>
       </c>
       <c r="E152" t="n">
-        <v>-1.672110038496012</v>
+        <v>-0.907310936337939</v>
       </c>
       <c r="F152" t="n">
-        <v>0.1284402944884</v>
+        <v>-0.05062965954675923</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>DR-81</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.6325557657442994</v>
+        <v>-1.015009306636397</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.09703754227106191</v>
+        <v>1.675828178112822</v>
       </c>
       <c r="D153" t="n">
-        <v>-1.941225205988132</v>
+        <v>-0.6528357095963063</v>
       </c>
       <c r="E153" t="n">
-        <v>-1.878237683024956</v>
+        <v>-0.5528708954993059</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.3309897329663597</v>
+        <v>-0.3429958612874077</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>DR-82</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.1153993507840051</v>
+        <v>-0.8102284222197501</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.205088694477435</v>
+        <v>-0.4076818547328841</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.4130603505602726</v>
+        <v>-0.4786786190230453</v>
       </c>
       <c r="E154" t="n">
-        <v>0.6817142655345553</v>
+        <v>-0.8393569231793807</v>
       </c>
       <c r="F154" t="n">
-        <v>0.8589729730069062</v>
+        <v>-0.2167715084964244</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>DR-83</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-0.7536201089289365</v>
+        <v>-1.00195484763293</v>
       </c>
       <c r="C155" t="n">
-        <v>0.3438074319282096</v>
+        <v>0.5131163687371264</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.2085333590898799</v>
+        <v>-0.5241394516036404</v>
       </c>
       <c r="E155" t="n">
-        <v>-0.2108227728146915</v>
+        <v>-0.3943344034513078</v>
       </c>
       <c r="F155" t="n">
-        <v>0.4940023650040606</v>
+        <v>-1.312762526563804</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>DR-84</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.007240738182834323</v>
+        <v>0.5144439613654356</v>
       </c>
       <c r="C156" t="n">
-        <v>0.6193423284371121</v>
+        <v>0.1763358292275429</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.7301590472524367</v>
+        <v>0.9836275108517822</v>
       </c>
       <c r="E156" t="n">
-        <v>0.1351735263653982</v>
+        <v>-0.8097912117703312</v>
       </c>
       <c r="F156" t="n">
-        <v>0.3846166020842425</v>
+        <v>2.589983836101797</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>DR-85</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>1.482541217114233</v>
+        <v>-0.9930873979351829</v>
       </c>
       <c r="C157" t="n">
-        <v>0.1868263964939311</v>
+        <v>0.5144178517496059</v>
       </c>
       <c r="D157" t="n">
-        <v>-1.547290955833628</v>
+        <v>-0.8441502957648388</v>
       </c>
       <c r="E157" t="n">
-        <v>-2.124830350892214</v>
+        <v>-0.6823691025249001</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.2516607626579916</v>
+        <v>-1.491843717667289</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-86</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-0.2837744012324309</v>
+        <v>-0.7963726196936579</v>
       </c>
       <c r="C158" t="n">
-        <v>0.5016547113687744</v>
+        <v>0.974534826986783</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.5970690720856117</v>
+        <v>1.091994787090341</v>
       </c>
       <c r="E158" t="n">
-        <v>0.4284759521481471</v>
+        <v>-0.6567917548213218</v>
       </c>
       <c r="F158" t="n">
-        <v>0.4510313141661224</v>
+        <v>-0.9488837254395595</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>DR-88</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1.355060870728787</v>
+        <v>0.0117526555472497</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.3013936793785994</v>
+        <v>-0.73985177196981</v>
       </c>
       <c r="D159" t="n">
-        <v>-1.836780301085543</v>
+        <v>-0.817289103690086</v>
       </c>
       <c r="E159" t="n">
-        <v>-2.426084646563067</v>
+        <v>-0.6338779173228389</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.2408559645366967</v>
+        <v>-0.1777276209309907</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>DR-89</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-0.3425388682196279</v>
+        <v>-1.579732221719511</v>
       </c>
       <c r="C160" t="n">
-        <v>0.1644068636919238</v>
+        <v>1.975716411257893</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.710471494567755</v>
+        <v>-0.4734271334271571</v>
       </c>
       <c r="E160" t="n">
-        <v>-0.3264694387999095</v>
+        <v>0.5956875930138472</v>
       </c>
       <c r="F160" t="n">
-        <v>0.6159328626848697</v>
+        <v>-0.1058681040928644</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-90</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.7375533769145141</v>
+        <v>-0.6744584092487215</v>
       </c>
       <c r="C161" t="n">
-        <v>0.5377470910102189</v>
+        <v>-0.2440638719742419</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.3155729594606045</v>
+        <v>-0.9117859169691628</v>
       </c>
       <c r="E161" t="n">
-        <v>0.3586479885718198</v>
+        <v>-0.6934853625024811</v>
       </c>
       <c r="F161" t="n">
-        <v>0.2512755157339018</v>
+        <v>0.324753125818087</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>S21(5)</t>
+          <t>DR-91</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-0.1192457301075725</v>
+        <v>1.021031092096627</v>
       </c>
       <c r="C162" t="n">
-        <v>-1.897752374499639</v>
+        <v>1.009359243429435</v>
       </c>
       <c r="D162" t="n">
-        <v>0.05411393523356423</v>
+        <v>1.217274769467989</v>
       </c>
       <c r="E162" t="n">
-        <v>0.5774896014064503</v>
+        <v>-0.6271253015348067</v>
       </c>
       <c r="F162" t="n">
-        <v>0.2437994158124216</v>
+        <v>-0.2751255759404679</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-92</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>-0.378460757545615</v>
+        <v>-2.110317859505462</v>
       </c>
       <c r="C163" t="n">
-        <v>0.487396704582196</v>
+        <v>-0.02058118170944797</v>
       </c>
       <c r="D163" t="n">
-        <v>-1.262967416508809</v>
+        <v>-0.1352274518528647</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.1345730381223933</v>
+        <v>0.2152172582641705</v>
       </c>
       <c r="F163" t="n">
-        <v>-0.3170888447862588</v>
+        <v>0.3576500913964213</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-93</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-0.6883082156051901</v>
+        <v>-0.7200847243088597</v>
       </c>
       <c r="C164" t="n">
-        <v>0.4201872601422895</v>
+        <v>0.2711962766439676</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.3879078965964933</v>
+        <v>-0.9484829920213043</v>
       </c>
       <c r="E164" t="n">
-        <v>0.2395905067631398</v>
+        <v>-0.4101939849464241</v>
       </c>
       <c r="F164" t="n">
-        <v>-0.2360079084768472</v>
+        <v>-0.3708419127645094</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.7909947827462699</v>
+        <v>-0.0664083053570174</v>
       </c>
       <c r="C165" t="n">
-        <v>2.558608577934677</v>
+        <v>0.3804218243122242</v>
       </c>
       <c r="D165" t="n">
-        <v>0.1687850886735982</v>
+        <v>-1.284453864195537</v>
       </c>
       <c r="E165" t="n">
-        <v>1.471757827089784</v>
+        <v>-0.8968105042536358</v>
       </c>
       <c r="F165" t="n">
-        <v>-2.461972662922924</v>
+        <v>0.1352004982798332</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-95</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-0.3474815956054845</v>
+        <v>-0.4375662871163732</v>
       </c>
       <c r="C166" t="n">
-        <v>0.827244496884092</v>
+        <v>0.7438386473655525</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.6914994516845722</v>
+        <v>-0.6856292156839224</v>
       </c>
       <c r="E166" t="n">
-        <v>0.6240190371314253</v>
+        <v>-0.273121773001928</v>
       </c>
       <c r="F166" t="n">
-        <v>-0.3873108614296547</v>
+        <v>-0.3097826238893269</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>DR-96</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-0.3698453355041255</v>
+        <v>-1.308391879954625</v>
       </c>
       <c r="C167" t="n">
-        <v>1.164421526613819</v>
+        <v>0.8590899584179612</v>
       </c>
       <c r="D167" t="n">
-        <v>0.08167139354063012</v>
+        <v>-1.611150919010674</v>
       </c>
       <c r="E167" t="n">
-        <v>-0.2739384666940013</v>
+        <v>-0.7718400991275056</v>
       </c>
       <c r="F167" t="n">
-        <v>0.2302511930260359</v>
+        <v>0.8179070920338987</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>S27(5)</t>
+          <t>DR-97</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-1.013449452795223</v>
+        <v>-0.7351209069725444</v>
       </c>
       <c r="C168" t="n">
-        <v>-1.570726895981475</v>
+        <v>1.343420209476699</v>
       </c>
       <c r="D168" t="n">
-        <v>0.0007081737756712605</v>
+        <v>-1.139269225581674</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.1352665450169949</v>
+        <v>-0.6745178152245933</v>
       </c>
       <c r="F168" t="n">
-        <v>-0.4580093189039053</v>
+        <v>0.4678942426930901</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-99</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-0.1842543984396828</v>
+        <v>1.890898730812354</v>
       </c>
       <c r="C169" t="n">
-        <v>1.228706790174722</v>
+        <v>0.4208949526761815</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.3700745561798187</v>
+        <v>-0.4239043013611681</v>
       </c>
       <c r="E169" t="n">
-        <v>0.4403730537445879</v>
+        <v>-0.5310460855914932</v>
       </c>
       <c r="F169" t="n">
-        <v>-1.319175953819443</v>
+        <v>1.850947894961372</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-100</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-1.166708458932659</v>
+        <v>-0.793008069402771</v>
       </c>
       <c r="C170" t="n">
-        <v>-1.868273717453426</v>
+        <v>1.667745206404922</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.4611380771034443</v>
+        <v>-1.160191406238646</v>
       </c>
       <c r="E170" t="n">
-        <v>0.02248209451929242</v>
+        <v>-0.615122661276107</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.8110211276092061</v>
+        <v>0.6062416853135359</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>DR-101</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-0.2798833086439018</v>
+        <v>0.2625850128299654</v>
       </c>
       <c r="C171" t="n">
-        <v>0.2221868975955128</v>
+        <v>2.283093246140577</v>
       </c>
       <c r="D171" t="n">
-        <v>-1.001146813516316</v>
+        <v>-0.1250219115643893</v>
       </c>
       <c r="E171" t="n">
-        <v>-0.04742051782874408</v>
+        <v>0.4955639157558782</v>
       </c>
       <c r="F171" t="n">
-        <v>0.3227666884856767</v>
+        <v>0.2610780338356148</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-102</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-1.108328995561727</v>
+        <v>-0.326329791013475</v>
       </c>
       <c r="C172" t="n">
-        <v>0.05014173164027312</v>
+        <v>0.6056550939708909</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.8310526584219826</v>
+        <v>-1.093886878835397</v>
       </c>
       <c r="E172" t="n">
-        <v>0.1219632869331452</v>
+        <v>-0.43968251076782</v>
       </c>
       <c r="F172" t="n">
-        <v>0.004081821624177833</v>
+        <v>-0.2088115335182164</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-0.8989315202919811</v>
+        <v>-0.9250303970103867</v>
       </c>
       <c r="C173" t="n">
-        <v>0.2167902276223424</v>
+        <v>1.030345030451903</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.9733750989813671</v>
+        <v>-1.513757009931917</v>
       </c>
       <c r="E173" t="n">
-        <v>0.1108687490320232</v>
+        <v>0.04046189144514506</v>
       </c>
       <c r="F173" t="n">
-        <v>-0.09957604781679011</v>
+        <v>0.5584231801733038</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>DR-104</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>-0.8289590100749287</v>
+        <v>-0.9983237916074064</v>
       </c>
       <c r="C174" t="n">
-        <v>0.2764081484637965</v>
+        <v>0.8661564495306826</v>
       </c>
       <c r="D174" t="n">
-        <v>-1.205915942776653</v>
+        <v>-1.0166002165358</v>
       </c>
       <c r="E174" t="n">
-        <v>0.2546803616991966</v>
+        <v>0.3043674709791668</v>
       </c>
       <c r="F174" t="n">
-        <v>-0.2130786850490974</v>
+        <v>0.7830275582158707</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-105</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-0.7602840750786108</v>
+        <v>-1.571029018094485</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.4444144649492485</v>
+        <v>1.621669948468071</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.8652700502517224</v>
+        <v>-0.6059204862174731</v>
       </c>
       <c r="E175" t="n">
-        <v>0.3227647515438087</v>
+        <v>0.02115023591656164</v>
       </c>
       <c r="F175" t="n">
-        <v>-0.08430759074540538</v>
+        <v>0.06034783458099952</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>DR-106</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.1603806362814416</v>
+        <v>-1.371457173039488</v>
       </c>
       <c r="C176" t="n">
-        <v>0.07316307268448029</v>
+        <v>1.538481545590026</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.7149495227564098</v>
+        <v>-0.8348807582756996</v>
       </c>
       <c r="E176" t="n">
-        <v>0.01256202430789051</v>
+        <v>0.3856926766319638</v>
       </c>
       <c r="F176" t="n">
-        <v>0.4309505796721009</v>
+        <v>0.02161471742200018</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>S40</t>
+          <t>DR-107</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.2026146551303367</v>
+        <v>0.2509493326992504</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.411558825530249</v>
+        <v>1.727043330575873</v>
       </c>
       <c r="D177" t="n">
-        <v>0.06156189467499287</v>
+        <v>-0.4977294052737344</v>
       </c>
       <c r="E177" t="n">
-        <v>0.9231637669043574</v>
+        <v>0.2420362879891709</v>
       </c>
       <c r="F177" t="n">
-        <v>1.094234780376258</v>
+        <v>0.6231270401053622</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>DR-108</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.4479711659430992</v>
+        <v>-0.7677711239436378</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.4027435759726622</v>
+        <v>-0.04010277874738502</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.1042272874080558</v>
+        <v>-0.4037107536805457</v>
       </c>
       <c r="E178" t="n">
-        <v>1.196418427948989</v>
+        <v>-0.3311535866417618</v>
       </c>
       <c r="F178" t="n">
-        <v>1.275046200043652</v>
+        <v>-2.0639742218003</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>DR-110</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>-1.27964735379897</v>
+        <v>-0.4961577293994748</v>
       </c>
       <c r="C179" t="n">
-        <v>0.09115000095249161</v>
+        <v>0.02032731071420807</v>
       </c>
       <c r="D179" t="n">
-        <v>0.243468385489473</v>
+        <v>-0.9617740582910286</v>
       </c>
       <c r="E179" t="n">
-        <v>-0.002725126993569148</v>
+        <v>-0.4175139246700573</v>
       </c>
       <c r="F179" t="n">
-        <v>0.2140081566494159</v>
+        <v>-0.6217979366477671</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>DR-111</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>-1.143942787547049</v>
+        <v>-1.048427612461274</v>
       </c>
       <c r="C180" t="n">
-        <v>0.02842720948995937</v>
+        <v>0.8171467118709845</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.1191458476233952</v>
+        <v>1.352691864977544</v>
       </c>
       <c r="E180" t="n">
-        <v>0.4203877385064491</v>
+        <v>-1.64482858644871</v>
       </c>
       <c r="F180" t="n">
-        <v>0.02287204505088429</v>
+        <v>-0.914331457354054</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>DR-112</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.5925651755558445</v>
+        <v>0.3347866437440328</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.1310733174697504</v>
+        <v>-0.3009805212877336</v>
       </c>
       <c r="D181" t="n">
-        <v>0.03611228618763456</v>
+        <v>0.3493291463748785</v>
       </c>
       <c r="E181" t="n">
-        <v>0.7865579297252785</v>
+        <v>-0.05570639361329726</v>
       </c>
       <c r="F181" t="n">
-        <v>1.820187407582679</v>
+        <v>-0.4112980846723511</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>DR-113</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-0.740698573694984</v>
+        <v>-0.3638673669825913</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.06116768331677921</v>
+        <v>0.7388918285397432</v>
       </c>
       <c r="D182" t="n">
-        <v>0.1460158069218132</v>
+        <v>-1.037838011748295</v>
       </c>
       <c r="E182" t="n">
-        <v>0.5235032012182124</v>
+        <v>-0.5487448389811025</v>
       </c>
       <c r="F182" t="n">
-        <v>0.3726584811491365</v>
+        <v>-0.2135456645689904</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>S46</t>
+          <t>DR-114</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>-1.86200958315026</v>
+        <v>-0.6201897912206977</v>
       </c>
       <c r="C183" t="n">
-        <v>0.2267570500665055</v>
+        <v>1.08143399963162</v>
       </c>
       <c r="D183" t="n">
-        <v>-0.0572361869769412</v>
+        <v>-0.9428650704122818</v>
       </c>
       <c r="E183" t="n">
-        <v>0.1437572397452882</v>
+        <v>-0.5273409492208067</v>
       </c>
       <c r="F183" t="n">
-        <v>0.4051078460949223</v>
+        <v>-0.3233092316697241</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>DR-115</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>-0.3987772645814109</v>
+        <v>1.249223683320098</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.4424777727600989</v>
+        <v>0.9272945991558535</v>
       </c>
       <c r="D184" t="n">
-        <v>0.07203301278281875</v>
+        <v>1.117283227963909</v>
       </c>
       <c r="E184" t="n">
-        <v>0.7927131973213964</v>
+        <v>-0.155387188739872</v>
       </c>
       <c r="F184" t="n">
-        <v>0.8001606452510946</v>
+        <v>2.376478204073889</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>DR-116</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>-0.05345155911196149</v>
+        <v>-0.7907914759421091</v>
       </c>
       <c r="C185" t="n">
-        <v>0.01168374465458051</v>
+        <v>0.8975819734255224</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.5410284259300312</v>
+        <v>-0.09005123066907886</v>
       </c>
       <c r="E185" t="n">
-        <v>0.4052175998878276</v>
+        <v>-0.2080427165179978</v>
       </c>
       <c r="F185" t="n">
-        <v>0.8039808134268657</v>
+        <v>-0.6947269691230796</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>DR-117</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-0.07683962053629081</v>
+        <v>-0.6234049605878589</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.8016799953515924</v>
+        <v>1.228459524692596</v>
       </c>
       <c r="D186" t="n">
-        <v>0.3385530080505831</v>
+        <v>2.203458113856034</v>
       </c>
       <c r="E186" t="n">
-        <v>0.6145147974707126</v>
+        <v>0.1139291784210246</v>
       </c>
       <c r="F186" t="n">
-        <v>0.8134779448242774</v>
+        <v>-0.3226209561664036</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>DR-118</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-0.7900559072583061</v>
+        <v>0.3912079220679889</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.3780292693768321</v>
+        <v>0.5736286600875536</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.003197297641703848</v>
+        <v>1.668289684770402</v>
       </c>
       <c r="E187" t="n">
-        <v>0.1130485605916831</v>
+        <v>-0.7260820558258029</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.6112661149013678</v>
+        <v>-0.5211938690761819</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>DR-119</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-0.8145098685722081</v>
+        <v>-0.9998206516892025</v>
       </c>
       <c r="C188" t="n">
-        <v>0.0457377911078377</v>
+        <v>0.9201494369545727</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.5447574739729534</v>
+        <v>0.7997692673567197</v>
       </c>
       <c r="E188" t="n">
-        <v>0.007495612440956036</v>
+        <v>-0.003384836216522041</v>
       </c>
       <c r="F188" t="n">
-        <v>0.195755713040905</v>
+        <v>-0.009086913755684092</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>DR-121</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>-0.7999828969989837</v>
+        <v>-1.008399407988076</v>
       </c>
       <c r="C189" t="n">
-        <v>0.2533666293672194</v>
+        <v>1.453044597940107</v>
       </c>
       <c r="D189" t="n">
-        <v>-1.221924355230072</v>
+        <v>0.8534122711425103</v>
       </c>
       <c r="E189" t="n">
-        <v>0.1985990948870276</v>
+        <v>-1.021433035090604</v>
       </c>
       <c r="F189" t="n">
-        <v>-0.3126619265870817</v>
+        <v>0.8542353144359023</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>DR-122</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>-0.1981338110111849</v>
+        <v>-1.842321979481718</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.3716298655545714</v>
+        <v>-0.7951376546704909</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.7797769107733762</v>
+        <v>-0.6630379355406965</v>
       </c>
       <c r="E190" t="n">
-        <v>0.4341838516437878</v>
+        <v>-1.190252916914434</v>
       </c>
       <c r="F190" t="n">
-        <v>0.3720949383631766</v>
+        <v>0.6037217709775715</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-123</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>-1.119178012925933</v>
+        <v>-0.03492809244605222</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.7220734958964805</v>
+        <v>-1.376818709065627</v>
       </c>
       <c r="D191" t="n">
-        <v>-1.243052680381563</v>
+        <v>-0.7018741088967463</v>
       </c>
       <c r="E191" t="n">
-        <v>0.07314958413137994</v>
+        <v>-0.5907119976396034</v>
       </c>
       <c r="F191" t="n">
-        <v>0.1476291077638085</v>
+        <v>0.02874951315438829</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-0.2481570869328451</v>
+        <v>1.32085826796013</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.762221149809616</v>
+        <v>-0.1221404271509152</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.7323033087310018</v>
+        <v>0.08493905890763009</v>
       </c>
       <c r="E192" t="n">
-        <v>0.5146809593099447</v>
+        <v>-0.1259869837026109</v>
       </c>
       <c r="F192" t="n">
-        <v>0.2606563336480834</v>
+        <v>-0.04250117072683722</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>LSC-01</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-0.3539561828061074</v>
+        <v>1.225543419309649</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.640828115983581</v>
+        <v>-0.2252310633348957</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.3244072765344935</v>
+        <v>0.2324529206030916</v>
       </c>
       <c r="E193" t="n">
-        <v>0.3234671346082518</v>
+        <v>0.3154282905241199</v>
       </c>
       <c r="F193" t="n">
-        <v>0.4440487705489903</v>
+        <v>0.05402046845475671</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>LSC-02</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.03579650184533321</v>
+        <v>1.215514307888973</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.6482296530161663</v>
+        <v>-0.4330321995575948</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.2325688959555662</v>
+        <v>-0.3014875251427269</v>
       </c>
       <c r="E194" t="n">
-        <v>-0.05993328176177665</v>
+        <v>-0.5181960153136619</v>
       </c>
       <c r="F194" t="n">
-        <v>0.02357573391034817</v>
+        <v>-0.3186810110788089</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>LSC-03</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>-0.3904733115518739</v>
+        <v>2.280249684972926</v>
       </c>
       <c r="C195" t="n">
-        <v>0.09001973239237138</v>
+        <v>-0.9044214655968287</v>
       </c>
       <c r="D195" t="n">
-        <v>0.243257510996019</v>
+        <v>-0.4336664252349414</v>
       </c>
       <c r="E195" t="n">
-        <v>1.149329568999445</v>
+        <v>-0.997794573809439</v>
       </c>
       <c r="F195" t="n">
-        <v>0.4158684041759503</v>
+        <v>0.740386861889526</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>S58</t>
+          <t>LSC-04</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.3959831139048317</v>
+        <v>0.9383701066128006</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.308569287604561</v>
+        <v>0.3454117304934839</v>
       </c>
       <c r="D196" t="n">
-        <v>0.004301446618495987</v>
+        <v>0.7132029556799712</v>
       </c>
       <c r="E196" t="n">
-        <v>0.728870864881938</v>
+        <v>-1.322184913261893</v>
       </c>
       <c r="F196" t="n">
-        <v>0.6943313900806198</v>
+        <v>-0.2381935624519998</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-0.3888140512869609</v>
+        <v>-1.923253453031258</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.6334254249549913</v>
+        <v>-0.8058418469356673</v>
       </c>
       <c r="D197" t="n">
-        <v>0.1771247215521554</v>
+        <v>-1.5228176050087</v>
       </c>
       <c r="E197" t="n">
-        <v>1.332648289060941</v>
+        <v>-1.639814999022414</v>
       </c>
       <c r="F197" t="n">
-        <v>1.207537301531832</v>
+        <v>0.2711778168433445</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>LSC-05</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>-0.6801278881941628</v>
+        <v>0.3049683365563426</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.5173110040623679</v>
+        <v>0.9040330102748043</v>
       </c>
       <c r="D198" t="n">
-        <v>0.09968775099881517</v>
+        <v>0.1868176783836593</v>
       </c>
       <c r="E198" t="n">
-        <v>1.2230646519692</v>
+        <v>1.107863757315208</v>
       </c>
       <c r="F198" t="n">
-        <v>0.3570041269403387</v>
+        <v>0.5977586786738055</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>LSC-06</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>-0.4538005434840531</v>
+        <v>0.8289384623469416</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.7000890407806775</v>
+        <v>-1.149618122598388</v>
       </c>
       <c r="D199" t="n">
-        <v>0.2943512354920546</v>
+        <v>1.018314645554286</v>
       </c>
       <c r="E199" t="n">
-        <v>1.072956842665642</v>
+        <v>0.8932075774929817</v>
       </c>
       <c r="F199" t="n">
-        <v>0.4410849132933069</v>
+        <v>-0.02317148783227307</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>SCR-03</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.0400682187433524</v>
+        <v>1.015704613411929</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.8032298827866906</v>
+        <v>0.6373488778247568</v>
       </c>
       <c r="D200" t="n">
-        <v>0.1733838714560963</v>
+        <v>0.555278314206328</v>
       </c>
       <c r="E200" t="n">
-        <v>0.4016772351917226</v>
+        <v>-0.2671078746262537</v>
       </c>
       <c r="F200" t="n">
-        <v>0.5814488368055888</v>
+        <v>-0.1661439097148171</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>S63</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.4675041812044795</v>
+        <v>0.934448903376956</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.7476424614325556</v>
+        <v>-0.0255262457776061</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.5021166230963514</v>
+        <v>-0.6694680543303435</v>
       </c>
       <c r="E201" t="n">
-        <v>-0.368359069618907</v>
+        <v>0.05203475441153892</v>
       </c>
       <c r="F201" t="n">
-        <v>0.4700646630734323</v>
+        <v>0.48253046761597</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>S64</t>
+          <t>DR-124</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>1.517796008483365</v>
+        <v>0.2344987561020826</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.4136747812907666</v>
+        <v>-0.6975672840846973</v>
       </c>
       <c r="D202" t="n">
-        <v>-1.652142977870346</v>
+        <v>0.7492248914681715</v>
       </c>
       <c r="E202" t="n">
-        <v>-2.228508189105935</v>
+        <v>-0.9251649023513702</v>
       </c>
       <c r="F202" t="n">
-        <v>0.1554014562935249</v>
+        <v>-0.1882659891262101</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>-0.7323742508485025</v>
+        <v>-1.405929261218391</v>
       </c>
       <c r="C203" t="n">
-        <v>0.04158885036263224</v>
+        <v>-1.319366655901647</v>
       </c>
       <c r="D203" t="n">
-        <v>-1.076831907216065</v>
+        <v>-0.8279051024975149</v>
       </c>
       <c r="E203" t="n">
-        <v>0.2492101901240651</v>
+        <v>-0.860490087963532</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.2411805003290617</v>
+        <v>-0.3662404119572452</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>S66</t>
+          <t>DR-126</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-1.130628774951365</v>
+        <v>0.02440567337561242</v>
       </c>
       <c r="C204" t="n">
-        <v>0.3876312767937488</v>
+        <v>-1.060885537313658</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.5893417690952742</v>
+        <v>-0.0009147919403415769</v>
       </c>
       <c r="E204" t="n">
-        <v>0.03652722884087044</v>
+        <v>-0.2822547030817896</v>
       </c>
       <c r="F204" t="n">
-        <v>0.876748166248295</v>
+        <v>0.4050476817856907</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>S67</t>
+          <t>LSC-08</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-0.858943728729073</v>
+        <v>-0.1349635121947528</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.08118924642044682</v>
+        <v>1.437271059579781</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.1605971726176749</v>
+        <v>0.04721730222072044</v>
       </c>
       <c r="E205" t="n">
-        <v>0.8034950460955185</v>
+        <v>1.271478978894267</v>
       </c>
       <c r="F205" t="n">
-        <v>0.3592372891403688</v>
+        <v>-0.02718401783003559</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>S68</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-0.836057260149892</v>
+        <v>0.6677250955451768</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.6313102256331975</v>
+        <v>3.035115590431638</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.5230210742185623</v>
+        <v>0.57255880132637</v>
       </c>
       <c r="E206" t="n">
-        <v>0.4009272854643441</v>
+        <v>-0.5658010094926155</v>
       </c>
       <c r="F206" t="n">
-        <v>0.2315457253210558</v>
+        <v>1.208489027964902</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>LSC-10</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>-1.593504621171649</v>
+        <v>-0.1893142383761824</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.2938466609380578</v>
+        <v>1.948600866161787</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.8668251392306695</v>
+        <v>0.8403255457316156</v>
       </c>
       <c r="E207" t="n">
-        <v>-0.0383563547598803</v>
+        <v>0.4328333464691886</v>
       </c>
       <c r="F207" t="n">
-        <v>0.631424551392256</v>
+        <v>-0.1888184757474311</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>LSC-11</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-0.06068328935201903</v>
+        <v>-1.12031719672636</v>
       </c>
       <c r="C208" t="n">
-        <v>0.05713970379422024</v>
+        <v>0.8250764157477725</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.9893368797384626</v>
+        <v>0.4204101318242425</v>
       </c>
       <c r="E208" t="n">
-        <v>0.2692107417241336</v>
+        <v>2.252724112905089</v>
       </c>
       <c r="F208" t="n">
-        <v>0.6722986771488113</v>
+        <v>0.8543018537456372</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>DR-127</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-0.5997916110866084</v>
+        <v>-0.838278262255771</v>
       </c>
       <c r="C209" t="n">
-        <v>0.2202615393776969</v>
+        <v>-0.07165264359759541</v>
       </c>
       <c r="D209" t="n">
-        <v>-1.245509576321554</v>
+        <v>-0.7142229324049325</v>
       </c>
       <c r="E209" t="n">
-        <v>-0.1278855012989412</v>
+        <v>0.05256156838661213</v>
       </c>
       <c r="F209" t="n">
-        <v>1.025369149026755</v>
+        <v>-0.6891382305510277</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>DR-128</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-0.2198195753894135</v>
+        <v>-1.920880686091268</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.4470148906886065</v>
+        <v>0.2525565763501503</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.3386038440995043</v>
+        <v>-0.2513572968988346</v>
       </c>
       <c r="E210" t="n">
-        <v>0.5197790091809332</v>
+        <v>0.4266552949139509</v>
       </c>
       <c r="F210" t="n">
-        <v>0.4075242719045125</v>
+        <v>-0.005748049370912628</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>S78</t>
+          <t>DR-129</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-0.2640472235311542</v>
+        <v>-0.9579654335703943</v>
       </c>
       <c r="C211" t="n">
-        <v>0.2125938599743068</v>
+        <v>0.6657714298416503</v>
       </c>
       <c r="D211" t="n">
-        <v>0.3008730802780937</v>
+        <v>-0.8411059090225177</v>
       </c>
       <c r="E211" t="n">
-        <v>0.8229038574086158</v>
+        <v>-0.2009981863744096</v>
       </c>
       <c r="F211" t="n">
-        <v>0.1999856011067053</v>
+        <v>-1.396823297657351</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.2550027031157554</v>
+        <v>0.3942562743216416</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.06129969061320299</v>
+        <v>2.831983437508672</v>
       </c>
       <c r="D212" t="n">
-        <v>-0.6599080964526013</v>
+        <v>-1.547083396049973</v>
       </c>
       <c r="E212" t="n">
-        <v>0.1786493385047458</v>
+        <v>0.5006973602775092</v>
       </c>
       <c r="F212" t="n">
-        <v>-0.112621032541309</v>
+        <v>0.6480320862745573</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>DR-130</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>-0.5403247991110428</v>
+        <v>-0.02846421947097869</v>
       </c>
       <c r="C213" t="n">
-        <v>0.1378721585693361</v>
+        <v>0.5108757313120815</v>
       </c>
       <c r="D213" t="n">
-        <v>-0.8113645311265216</v>
+        <v>-0.1154756043553404</v>
       </c>
       <c r="E213" t="n">
-        <v>0.3936132814383531</v>
+        <v>-1.190840610017268</v>
       </c>
       <c r="F213" t="n">
-        <v>-0.0343380487921119</v>
+        <v>0.09743847638927167</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>S80</t>
+          <t>DR-132</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.6004218807183793</v>
+        <v>-0.2641906344378903</v>
       </c>
       <c r="C214" t="n">
-        <v>0.2948872719191594</v>
+        <v>0.3313744327793325</v>
       </c>
       <c r="D214" t="n">
-        <v>0.04296431605503376</v>
+        <v>-1.202179111528272</v>
       </c>
       <c r="E214" t="n">
-        <v>0.3526513476079619</v>
+        <v>-0.3540013794560449</v>
       </c>
       <c r="F214" t="n">
-        <v>0.1578310194274455</v>
+        <v>-0.3612964062415035</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>DR-133</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>1.481298200754268</v>
+        <v>0.8778869692769407</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.2012428171232764</v>
+        <v>-0.1666580879385423</v>
       </c>
       <c r="D215" t="n">
-        <v>-1.750633425974419</v>
+        <v>-0.7859204615219314</v>
       </c>
       <c r="E215" t="n">
-        <v>-1.868358098065273</v>
+        <v>-0.6446609268853587</v>
       </c>
       <c r="F215" t="n">
-        <v>-0.9701341736048034</v>
+        <v>0.2483297968996498</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>DR-134</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.04173405787895559</v>
+        <v>-0.9832389077190614</v>
       </c>
       <c r="C216" t="n">
-        <v>0.6457119672386447</v>
+        <v>0.2031533571006578</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.8248102336695033</v>
+        <v>-0.8670339600935338</v>
       </c>
       <c r="E216" t="n">
-        <v>0.1904244817460253</v>
+        <v>-0.7903117820297235</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.3673460281011682</v>
+        <v>-0.4141846972556929</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>S83</t>
+          <t>DR-135</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>3.485936184375646</v>
+        <v>0.502846670395507</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.2845162427247176</v>
+        <v>2.022202132660183</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.7781892494017375</v>
+        <v>0.251416161709998</v>
       </c>
       <c r="E217" t="n">
-        <v>-1.564618361609401</v>
+        <v>0.2804858371498278</v>
       </c>
       <c r="F217" t="n">
-        <v>0.7737150835737626</v>
+        <v>0.6364639866338487</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>S84</t>
+          <t>DR-136</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>-0.02655415116838269</v>
+        <v>0.07690009361801158</v>
       </c>
       <c r="C218" t="n">
-        <v>0.7994443379792253</v>
+        <v>0.3969856616887658</v>
       </c>
       <c r="D218" t="n">
-        <v>0.614956841420542</v>
+        <v>-0.8444774554135355</v>
       </c>
       <c r="E218" t="n">
-        <v>-1.493311877406757</v>
+        <v>-0.5978106992815555</v>
       </c>
       <c r="F218" t="n">
-        <v>-0.3317472428458874</v>
+        <v>0.08700039879641851</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>S85</t>
+          <t>LSC-13</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.1623579943907998</v>
+        <v>0.06144242617292715</v>
       </c>
       <c r="C219" t="n">
-        <v>0.2989261115617977</v>
+        <v>1.672740658478363</v>
       </c>
       <c r="D219" t="n">
-        <v>0.4345506317210071</v>
+        <v>0.4377147921145754</v>
       </c>
       <c r="E219" t="n">
-        <v>0.02580370422115483</v>
+        <v>0.5526192994050833</v>
       </c>
       <c r="F219" t="n">
-        <v>0.198436126978552</v>
+        <v>-0.1757615389996049</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>S87</t>
+          <t>DR-137</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>3.10066401448596</v>
+        <v>-0.5284334598887348</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.1842059266168907</v>
+        <v>1.006952859406915</v>
       </c>
       <c r="D220" t="n">
-        <v>-0.2846428520128291</v>
+        <v>-0.1283910776574466</v>
       </c>
       <c r="E220" t="n">
-        <v>-1.520153815923189</v>
+        <v>-0.5255675230178976</v>
       </c>
       <c r="F220" t="n">
-        <v>0.643807864305359</v>
+        <v>-0.5164512738657118</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>S89</t>
+          <t>DR-138</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.4128965206102206</v>
+        <v>-1.231032521872362</v>
       </c>
       <c r="C221" t="n">
-        <v>0.03386530586807054</v>
+        <v>0.7384525050094918</v>
       </c>
       <c r="D221" t="n">
-        <v>0.9031678846560364</v>
+        <v>1.13752349867676</v>
       </c>
       <c r="E221" t="n">
-        <v>0.4673656982857752</v>
+        <v>-1.063492550451059</v>
       </c>
       <c r="F221" t="n">
-        <v>0.7894809257110943</v>
+        <v>0.05113789274759804</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>DR-139</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.0960077991113934</v>
+        <v>0.1603909875026305</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.05096128792001761</v>
+        <v>0.5225671107758427</v>
       </c>
       <c r="D222" t="n">
-        <v>-0.6015070710514404</v>
+        <v>-0.8413990367241897</v>
       </c>
       <c r="E222" t="n">
-        <v>0.717231081033961</v>
+        <v>-0.5645558901500682</v>
       </c>
       <c r="F222" t="n">
-        <v>0.5018781137036387</v>
+        <v>-0.0852273236001648</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>S90</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>2.667663033563954</v>
+        <v>0.4247083557179378</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.3450683157972566</v>
+        <v>-0.2552515639190211</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.8715157992570992</v>
+        <v>-0.9742092315620718</v>
       </c>
       <c r="E223" t="n">
-        <v>-1.464710194937623</v>
+        <v>0.6524330022247664</v>
       </c>
       <c r="F223" t="n">
-        <v>0.3930885911159451</v>
+        <v>0.6010513172693848</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>S93</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.1867277206334193</v>
+        <v>1.161468198494765</v>
       </c>
       <c r="C224" t="n">
-        <v>0.3984140380851148</v>
+        <v>-0.3318853650384914</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.5055164108894176</v>
+        <v>-0.8383891229430238</v>
       </c>
       <c r="E224" t="n">
-        <v>-1.328244003211134</v>
+        <v>0.1101304044667056</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.4291105942868691</v>
+        <v>-0.2348356756122667</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>S94</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>-0.5450984271941114</v>
+        <v>0.5640713903793989</v>
       </c>
       <c r="C225" t="n">
-        <v>0.4158723331737255</v>
+        <v>-0.03007941950342956</v>
       </c>
       <c r="D225" t="n">
-        <v>0.3633649591590681</v>
+        <v>-0.2974923883391676</v>
       </c>
       <c r="E225" t="n">
-        <v>-0.8739318969196624</v>
+        <v>0.2832377768354875</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.2091212712193194</v>
+        <v>-0.3255059940074121</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>S95</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>3.26779990569544</v>
+        <v>-0.2084084057632229</v>
       </c>
       <c r="C226" t="n">
-        <v>-3.152761339160422</v>
+        <v>-1.035838319338743</v>
       </c>
       <c r="D226" t="n">
-        <v>0.2842162875561738</v>
+        <v>-0.07145055095498211</v>
       </c>
       <c r="E226" t="n">
-        <v>-0.8869393265953808</v>
+        <v>0.5961933739452944</v>
       </c>
       <c r="F226" t="n">
-        <v>-1.101346250329599</v>
+        <v>0.3625187425778215</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>S96</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>-0.861603529006887</v>
+        <v>-0.6792538828463366</v>
       </c>
       <c r="C227" t="n">
-        <v>0.04040969167696268</v>
+        <v>-1.081157415414523</v>
       </c>
       <c r="D227" t="n">
-        <v>-1.272069838286076</v>
+        <v>-1.64887612444878</v>
       </c>
       <c r="E227" t="n">
-        <v>0.1003878796833057</v>
+        <v>-2.205392142732536</v>
       </c>
       <c r="F227" t="n">
-        <v>-0.07872704828221073</v>
+        <v>-0.218099585143699</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>S97</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>-0.418366949674098</v>
+        <v>0.571027152582922</v>
       </c>
       <c r="C228" t="n">
-        <v>0.2656618029644081</v>
+        <v>0.3874531276051407</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.7101196882623635</v>
+        <v>-0.8420351119869485</v>
       </c>
       <c r="E228" t="n">
-        <v>0.2898614199157161</v>
+        <v>0.3763780776337093</v>
       </c>
       <c r="F228" t="n">
-        <v>-0.4767922358849133</v>
+        <v>-0.6083502380549303</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>S98</t>
+          <t>SCR-12</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>-1.554261942046767</v>
+        <v>-1.820106160795446</v>
       </c>
       <c r="C229" t="n">
-        <v>0.7733328209918877</v>
+        <v>-0.7871990835894634</v>
       </c>
       <c r="D229" t="n">
-        <v>1.240401452129216</v>
+        <v>-1.211081749352829</v>
       </c>
       <c r="E229" t="n">
-        <v>-0.7196134885529213</v>
+        <v>-1.32224038658892</v>
       </c>
       <c r="F229" t="n">
-        <v>-0.00262504393449086</v>
+        <v>0.5704317035890912</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>S99</t>
+          <t>SCR-13</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.8620026481151176</v>
+        <v>-0.415051430389828</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.04959344271390201</v>
+        <v>-0.2244246824312897</v>
       </c>
       <c r="D230" t="n">
-        <v>-2.257908744240551</v>
+        <v>-1.849672912446776</v>
       </c>
       <c r="E230" t="n">
-        <v>-2.223943011130332</v>
+        <v>-1.830675556543718</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.1320626303912797</v>
+        <v>0.1772449528419238</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>UBC1</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>-1.899162021735144</v>
+        <v>0.1393738660030946</v>
       </c>
       <c r="C231" t="n">
-        <v>-1.025870120641256</v>
+        <v>-0.3808276384228949</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.2727705169980677</v>
+        <v>-0.3879335634564727</v>
       </c>
       <c r="E231" t="n">
-        <v>-0.1260160931276808</v>
+        <v>1.002502588604463</v>
       </c>
       <c r="F231" t="n">
-        <v>0.1684165364273268</v>
+        <v>0.7408586878296329</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>UCC1</t>
+          <t>SCR-15</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>-1.63553129634541</v>
+        <v>0.983865311315533</v>
       </c>
       <c r="C232" t="n">
-        <v>-1.395298216260744</v>
+        <v>0.1138640025813092</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.08579640407348338</v>
+        <v>-0.09273460060424485</v>
       </c>
       <c r="E232" t="n">
-        <v>-0.2601994772803401</v>
+        <v>-0.05269120571154685</v>
       </c>
       <c r="F232" t="n">
-        <v>-0.1857242182016914</v>
+        <v>0.5198211831719092</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>UCE1</t>
+          <t>SCR-16</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>-0.1745709921678751</v>
+        <v>0.6834605604897224</v>
       </c>
       <c r="C233" t="n">
-        <v>-1.712263188522721</v>
+        <v>-0.7302002314062458</v>
       </c>
       <c r="D233" t="n">
-        <v>-0.07759539303533097</v>
+        <v>-0.5780185991779199</v>
       </c>
       <c r="E233" t="n">
-        <v>-0.06871941733346525</v>
+        <v>0.1108513093725992</v>
       </c>
       <c r="F233" t="n">
-        <v>-0.0002854406845296353</v>
+        <v>0.4043745259240101</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>UJC1</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>-1.743287985342949</v>
+        <v>-0.9817800786404681</v>
       </c>
       <c r="C234" t="n">
-        <v>-1.568508225312921</v>
+        <v>-0.896360225117574</v>
       </c>
       <c r="D234" t="n">
-        <v>0.4782668916184202</v>
+        <v>-1.377146883959467</v>
       </c>
       <c r="E234" t="n">
-        <v>0.2962338421606491</v>
+        <v>-2.096177624653828</v>
       </c>
       <c r="F234" t="n">
-        <v>-0.4807126353791843</v>
+        <v>0.2968292796972613</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>SCR-18</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>0.8692406433345827</v>
+      </c>
+      <c r="C235" t="n">
+        <v>-0.5217693328914134</v>
+      </c>
+      <c r="D235" t="n">
+        <v>-0.4803918025734784</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0.4472174300243796</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0.39730514917695</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>SCR-19</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>-1.202122240017549</v>
+      </c>
+      <c r="C236" t="n">
+        <v>-0.4248993667871844</v>
+      </c>
+      <c r="D236" t="n">
+        <v>-1.732285918384331</v>
+      </c>
+      <c r="E236" t="n">
+        <v>-2.253372353927938</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0.3773080331206595</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>SCR-20</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>0.5835849830968176</v>
+      </c>
+      <c r="C237" t="n">
+        <v>-0.0603556252773828</v>
+      </c>
+      <c r="D237" t="n">
+        <v>-0.5960054066236147</v>
+      </c>
+      <c r="E237" t="n">
+        <v>-0.1226223470731344</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0.7033590317102842</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>LSC-14</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>0.07810453014706399</v>
+      </c>
+      <c r="C238" t="n">
+        <v>-1.200962123206352</v>
+      </c>
+      <c r="D238" t="n">
+        <v>-0.194170975420789</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0.338464742304821</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0.2225141988771634</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>LSC-15</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>-0.7332499248661906</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.9855546994074253</v>
+      </c>
+      <c r="D239" t="n">
+        <v>-0.2709309355078321</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1.290517321101279</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0.1143095021589842</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>LSC-16</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>0.94453603191174</v>
+      </c>
+      <c r="C240" t="n">
+        <v>-0.3423091228930936</v>
+      </c>
+      <c r="D240" t="n">
+        <v>-1.185478100001358</v>
+      </c>
+      <c r="E240" t="n">
+        <v>-0.3162372004346363</v>
+      </c>
+      <c r="F240" t="n">
+        <v>-0.2030060628913128</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>LSC-17</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>1.114525277482655</v>
+      </c>
+      <c r="C241" t="n">
+        <v>-0.1137141146725427</v>
+      </c>
+      <c r="D241" t="n">
+        <v>-0.34815568253028</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0.1465896530165204</v>
+      </c>
+      <c r="F241" t="n">
+        <v>-0.2612057256150683</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>LSC-18</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1.546711371441591</v>
+      </c>
+      <c r="C242" t="n">
+        <v>-2.825743681220268</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.3191867212212897</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0.1483929536485605</v>
+      </c>
+      <c r="F242" t="n">
+        <v>-2.648209077518965</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>LSC-19</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>1.203023172926712</v>
+      </c>
+      <c r="C243" t="n">
+        <v>-0.7492469061624483</v>
+      </c>
+      <c r="D243" t="n">
+        <v>-0.6079002703728205</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0.3184169436427344</v>
+      </c>
+      <c r="F243" t="n">
+        <v>-0.4491439015008379</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>LSC-20</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1.159274009347735</v>
+      </c>
+      <c r="C244" t="n">
+        <v>-0.65299567747897</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.3196566479029095</v>
+      </c>
+      <c r="E244" t="n">
+        <v>-0.3952801935270973</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0.2693257666599246</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>LSC-21</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>0.0713992951008787</v>
+      </c>
+      <c r="C245" t="n">
+        <v>1.577727467617044</v>
+      </c>
+      <c r="D245" t="n">
+        <v>-0.3103207378585116</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0.3622320440480178</v>
+      </c>
+      <c r="F245" t="n">
+        <v>-0.4528541891011301</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>LSC-22</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>1.307100596428844</v>
+      </c>
+      <c r="C246" t="n">
+        <v>-1.042632558787025</v>
+      </c>
+      <c r="D246" t="n">
+        <v>-0.2959858000611038</v>
+      </c>
+      <c r="E246" t="n">
+        <v>-0.1741776566370134</v>
+      </c>
+      <c r="F246" t="n">
+        <v>-1.337775537503489</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>LSC-23</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0.1015399803045509</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1.802382336296259</v>
+      </c>
+      <c r="D247" t="n">
+        <v>-0.8620635788008572</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0.4706647516312362</v>
+      </c>
+      <c r="F247" t="n">
+        <v>-0.8004653898275575</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>SCR-05</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0.6630519403733542</v>
+      </c>
+      <c r="C248" t="n">
+        <v>-0.2404095922067395</v>
+      </c>
+      <c r="D248" t="n">
+        <v>-0.9149019559689769</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0.02184652585052342</v>
+      </c>
+      <c r="F248" t="n">
+        <v>0.3871789769977609</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>LSC-24</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>1.224372516610434</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.4136441693704949</v>
+      </c>
+      <c r="D249" t="n">
+        <v>-0.8281023628580773</v>
+      </c>
+      <c r="E249" t="n">
+        <v>0.17109958196545</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0.01198330809236472</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>LSC-25</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>1.18213600754334</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.1506301341842466</v>
+      </c>
+      <c r="D250" t="n">
+        <v>-0.9461752482941327</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0.07279941982613823</v>
+      </c>
+      <c r="F250" t="n">
+        <v>-0.07112368851550047</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>LSC-26</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>1.218376231304476</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.004640734886572448</v>
+      </c>
+      <c r="D251" t="n">
+        <v>-1.183174029910725</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0.1405601178578784</v>
+      </c>
+      <c r="F251" t="n">
+        <v>-0.1907700649106444</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>LSC-27</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>0.7014174134608344</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.4484021671809582</v>
+      </c>
+      <c r="D252" t="n">
+        <v>-0.9597898516483812</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.4748456537691315</v>
+      </c>
+      <c r="F252" t="n">
+        <v>-0.1034096103542134</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>SCR-06</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0.2112094924415941</v>
+      </c>
+      <c r="C253" t="n">
+        <v>-0.4357237266350313</v>
+      </c>
+      <c r="D253" t="n">
+        <v>-0.6431096578841232</v>
+      </c>
+      <c r="E253" t="n">
+        <v>0.1686686397565412</v>
+      </c>
+      <c r="F253" t="n">
+        <v>0.4721649945093902</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>LSC-28</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>-0.07070169668384843</v>
+      </c>
+      <c r="C254" t="n">
+        <v>-0.3306373605644949</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.0571193674267929</v>
+      </c>
+      <c r="E254" t="n">
+        <v>1.384438209879155</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0.8938176834370131</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>LSC-29</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>-0.2000922920461045</v>
+      </c>
+      <c r="C255" t="n">
+        <v>-0.5955598732643618</v>
+      </c>
+      <c r="D255" t="n">
+        <v>-0.09898253998262255</v>
+      </c>
+      <c r="E255" t="n">
+        <v>1.664245744051486</v>
+      </c>
+      <c r="F255" t="n">
+        <v>1.036204526870242</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>LSC-30</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>1.24096204549042</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.6275255112978453</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.2657113208346332</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0.1871075412452188</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0.1631347432788183</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>LSC-31</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>1.217980678793603</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.4312888023601326</v>
+      </c>
+      <c r="D257" t="n">
+        <v>-0.1418634155990458</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0.5191344301213402</v>
+      </c>
+      <c r="F257" t="n">
+        <v>-0.07459990569469176</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>LSC-32</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>-0.2608960721840972</v>
+      </c>
+      <c r="C258" t="n">
+        <v>-0.757133082344878</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0.1612940429533529</v>
+      </c>
+      <c r="E258" t="n">
+        <v>1.350048901272413</v>
+      </c>
+      <c r="F258" t="n">
+        <v>1.639426124895846</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>LSC-33</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>0.8268193000548197</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.2056805975468095</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0.1389993079880733</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0.7468284499346713</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0.2384579774181891</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>LSC-34</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>1.814403578856385</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.8684703639858982</v>
+      </c>
+      <c r="D260" t="n">
+        <v>-0.0079235269603128</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0.3096103535032906</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0.3283879575226757</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>LSC-35</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>0.3646559071747472</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.1418185872186762</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0.0318691533334333</v>
+      </c>
+      <c r="E261" t="n">
+        <v>1.20516418527123</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0.6158917067266014</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>LSC-36</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>0.3680579907756264</v>
+      </c>
+      <c r="C262" t="n">
+        <v>-0.344493903735568</v>
+      </c>
+      <c r="D262" t="n">
+        <v>-0.4707819168128668</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0.6594288091732353</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0.744632106480963</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>LSC-37</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>-0.1570146923196112</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.2326310969253575</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0.2500224688860147</v>
+      </c>
+      <c r="E263" t="n">
+        <v>1.168375098090928</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0.6502100166515313</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>SCR-07</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>0.6711699765497344</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.5606049042622211</v>
+      </c>
+      <c r="D264" t="n">
+        <v>-0.1340244003386021</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0.2033307535077257</v>
+      </c>
+      <c r="F264" t="n">
+        <v>-0.6360205089529064</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>LSC-38</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>0.9377377161198525</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.2691226355922604</v>
+      </c>
+      <c r="D265" t="n">
+        <v>-0.5168326888787014</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0.1355056916509903</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0.2080446019660457</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>LSC-39</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>1.179597925896031</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.01515012695787869</v>
+      </c>
+      <c r="D266" t="n">
+        <v>-1.208845029352035</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0.06908935653425451</v>
+      </c>
+      <c r="F266" t="n">
+        <v>-0.2755975655206065</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>LSC-40</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>0.2998384326599359</v>
+      </c>
+      <c r="C267" t="n">
+        <v>-0.01329189361499503</v>
+      </c>
+      <c r="D267" t="n">
+        <v>-0.8168602637599788</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0.6727302615367481</v>
+      </c>
+      <c r="F267" t="n">
+        <v>0.3289466529452807</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>LSC-41</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>0.7914145394309022</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.9139675370877934</v>
+      </c>
+      <c r="D268" t="n">
+        <v>-1.352068195060044</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0.3528888967746545</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0.1841458021013693</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>LSC-42</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0.1175969007586673</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.265069839342911</v>
+      </c>
+      <c r="D269" t="n">
+        <v>-0.8521570881031894</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0.8386084782074297</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0.1987187395563254</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>LSC-43</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>0.1887472399707994</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.3419424286921014</v>
+      </c>
+      <c r="D270" t="n">
+        <v>-0.4022088350544251</v>
+      </c>
+      <c r="E270" t="n">
+        <v>0.7061821021769598</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0.3835724657938435</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>LSC-44</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>-0.1669506112438173</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.1967349504565019</v>
+      </c>
+      <c r="D271" t="n">
+        <v>-0.3254066255978272</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0.2534949659222784</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0.04922928716693498</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>0.7446786226019569</v>
+      </c>
+      <c r="C272" t="n">
+        <v>-0.2991903401078189</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0.2377730792736488</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1.299307031392691</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0.1665640223666352</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>LSC-46</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>-0.1629018824745216</v>
+      </c>
+      <c r="C273" t="n">
+        <v>-0.4797619448288858</v>
+      </c>
+      <c r="D273" t="n">
+        <v>-0.005965543184625438</v>
+      </c>
+      <c r="E273" t="n">
+        <v>1.068853342555741</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0.5499337652895244</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>0.3018715307876982</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.1195507550752042</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0.1129948468191639</v>
+      </c>
+      <c r="E274" t="n">
+        <v>1.87147521049779</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0.9037884647023795</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>0.6304987173048353</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.2733348960849845</v>
+      </c>
+      <c r="D275" t="n">
+        <v>-0.02224288689243017</v>
+      </c>
+      <c r="E275" t="n">
+        <v>1.521118385517884</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0.09450702804619426</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>LSC-49</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>0.2968197579116274</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.2972782374528394</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0.1585685104085309</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1.470888768429926</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0.1959454568566088</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>LSC-50</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>-0.25518486005028</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.2000391297410782</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0.07771557826661502</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0.8992199690830156</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0.4780856411049083</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>LSC-51</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>-0.608555209483055</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.02447707139772402</v>
+      </c>
+      <c r="D278" t="n">
+        <v>-0.5441681814035739</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0.08099974210194633</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0.5701803988021577</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>LSC-52</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>-1.400711902126963</v>
+      </c>
+      <c r="C279" t="n">
+        <v>-0.5036900291695083</v>
+      </c>
+      <c r="D279" t="n">
+        <v>-1.539506401577822</v>
+      </c>
+      <c r="E279" t="n">
+        <v>-1.924882659763999</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0.7172684267863324</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>0.9902679965039481</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.1081315482800703</v>
+      </c>
+      <c r="D280" t="n">
+        <v>-1.09637400271551</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0.2074494402389253</v>
+      </c>
+      <c r="F280" t="n">
+        <v>-0.2247367461262689</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>LSC-54</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>1.35920712113773</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.2390153758920658</v>
+      </c>
+      <c r="D281" t="n">
+        <v>-0.4454221379565815</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.2293698123548213</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0.8628942716914628</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>0.9847376268523387</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.1973112362473241</v>
+      </c>
+      <c r="D282" t="n">
+        <v>-0.185781109529095</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0.9841740224349529</v>
+      </c>
+      <c r="F282" t="n">
+        <v>0.1906793869157701</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0.6090154989028176</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.6299537784010764</v>
+      </c>
+      <c r="D283" t="n">
+        <v>-0.62886727382978</v>
+      </c>
+      <c r="E283" t="n">
+        <v>0.7095990555874916</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0.1635474660293843</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>1.331124384929669</v>
+      </c>
+      <c r="C284" t="n">
+        <v>1.01097531873043</v>
+      </c>
+      <c r="D284" t="n">
+        <v>-0.8630360116975616</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0.278948983824539</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0.6413238010160635</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>0.4294291752788226</v>
+      </c>
+      <c r="C285" t="n">
+        <v>-0.3695901676173359</v>
+      </c>
+      <c r="D285" t="n">
+        <v>-0.9119163201089704</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0.4496937503772678</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0.672159430156371</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0.8798125321469047</v>
+      </c>
+      <c r="C286" t="n">
+        <v>-0.02538582184523294</v>
+      </c>
+      <c r="D286" t="n">
+        <v>-1.092262265856247</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0.1033930796195041</v>
+      </c>
+      <c r="F286" t="n">
+        <v>1.095019402929188</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0.2398692040475287</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.06577538208451536</v>
+      </c>
+      <c r="D287" t="n">
+        <v>-0.3947154992841819</v>
+      </c>
+      <c r="E287" t="n">
+        <v>0.8202782230671076</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0.3166914661151142</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>LSC-61</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0.6716037397375018</v>
+      </c>
+      <c r="C288" t="n">
+        <v>-0.3712537590475603</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0.3148188367047809</v>
+      </c>
+      <c r="E288" t="n">
+        <v>0.9111107292879194</v>
+      </c>
+      <c r="F288" t="n">
+        <v>0.01728919477342692</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>0.1099131702944834</v>
+      </c>
+      <c r="C289" t="n">
+        <v>-0.4463306073376599</v>
+      </c>
+      <c r="D289" t="n">
+        <v>-0.6697066898367138</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0.2315867730463096</v>
+      </c>
+      <c r="F289" t="n">
+        <v>-0.09040221518174009</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>0.8881721328879399</v>
+      </c>
+      <c r="C290" t="n">
+        <v>-0.1068207186842545</v>
+      </c>
+      <c r="D290" t="n">
+        <v>-0.8023711285528893</v>
+      </c>
+      <c r="E290" t="n">
+        <v>0.3852633139608479</v>
+      </c>
+      <c r="F290" t="n">
+        <v>-0.0628732151088388</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>LSC-63</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>0.005128111103866774</v>
+      </c>
+      <c r="C291" t="n">
+        <v>-0.9115217802449059</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0.1084690816983461</v>
+      </c>
+      <c r="E291" t="n">
+        <v>0.4121385117861708</v>
+      </c>
+      <c r="F291" t="n">
+        <v>0.1036263624147822</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>-1.111902063877051</v>
+      </c>
+      <c r="C292" t="n">
+        <v>-0.7169122783667162</v>
+      </c>
+      <c r="D292" t="n">
+        <v>-1.725487642360105</v>
+      </c>
+      <c r="E292" t="n">
+        <v>-1.939432055921128</v>
+      </c>
+      <c r="F292" t="n">
+        <v>-0.4393462803525808</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>0.7325465005736872</v>
+      </c>
+      <c r="C293" t="n">
+        <v>-0.7874248470337186</v>
+      </c>
+      <c r="D293" t="n">
+        <v>-0.7398594420515363</v>
+      </c>
+      <c r="E293" t="n">
+        <v>-0.03984276041787253</v>
+      </c>
+      <c r="F293" t="n">
+        <v>-0.3309237201221508</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>DR-146</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>-2.839617779094396</v>
+      </c>
+      <c r="C294" t="n">
+        <v>-2.052732842108686</v>
+      </c>
+      <c r="D294" t="n">
+        <v>-0.5979813491112995</v>
+      </c>
+      <c r="E294" t="n">
+        <v>-1.135200303070286</v>
+      </c>
+      <c r="F294" t="n">
+        <v>1.186215559881198</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>DR-147</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0.4437299601034582</v>
+      </c>
+      <c r="C295" t="n">
+        <v>-0.2591184839826174</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0.802266084872383</v>
+      </c>
+      <c r="E295" t="n">
+        <v>-1.516187654108353</v>
+      </c>
+      <c r="F295" t="n">
+        <v>-0.07953522279401419</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>DR-148</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>0.2465119832317057</v>
+      </c>
+      <c r="C296" t="n">
+        <v>-0.4912584715359157</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0.5106453440155375</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0.154081760141054</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0.1669157544576713</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>DR-149</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>-2.517828369669152</v>
+      </c>
+      <c r="C297" t="n">
+        <v>-1.824472514733394</v>
+      </c>
+      <c r="D297" t="n">
+        <v>-0.1131173712241458</v>
+      </c>
+      <c r="E297" t="n">
+        <v>-1.111008458418682</v>
+      </c>
+      <c r="F297" t="n">
+        <v>1.008985823715207</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>DR-150</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>-0.1086092318668096</v>
+      </c>
+      <c r="C298" t="n">
+        <v>-0.572710097447639</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0.9650896940414991</v>
+      </c>
+      <c r="E298" t="n">
+        <v>0.8250684796318131</v>
+      </c>
+      <c r="F298" t="n">
+        <v>0.6331314276490958</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>0.2914705030305319</v>
+      </c>
+      <c r="C299" t="n">
+        <v>-0.4928951427874476</v>
+      </c>
+      <c r="D299" t="n">
+        <v>-0.5836441828263941</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0.886262358483766</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0.3995330737185449</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>DR-151</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>-2.201173576318704</v>
+      </c>
+      <c r="C300" t="n">
+        <v>-1.48298179928871</v>
+      </c>
+      <c r="D300" t="n">
+        <v>-0.7547611625382463</v>
+      </c>
+      <c r="E300" t="n">
+        <v>-1.120623605175074</v>
+      </c>
+      <c r="F300" t="n">
+        <v>0.7823499865242027</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>DR-152</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>0.1830295671763576</v>
+      </c>
+      <c r="C301" t="n">
+        <v>-0.2772628693705321</v>
+      </c>
+      <c r="D301" t="n">
+        <v>-0.3895220997229363</v>
+      </c>
+      <c r="E301" t="n">
+        <v>-1.365637962228532</v>
+      </c>
+      <c r="F301" t="n">
+        <v>-0.1264703879724374</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>DR-154</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>0.7347902803631162</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.1601901412131471</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0.4581237650516288</v>
+      </c>
+      <c r="E302" t="n">
+        <v>-0.8162427880311486</v>
+      </c>
+      <c r="F302" t="n">
+        <v>-0.0740157634995294</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>DR-155</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>-4.291252371019447</v>
+      </c>
+      <c r="C303" t="n">
+        <v>-0.06353464974984996</v>
+      </c>
+      <c r="D303" t="n">
+        <v>-0.2517916489106851</v>
+      </c>
+      <c r="E303" t="n">
+        <v>-0.03921000250052561</v>
+      </c>
+      <c r="F303" t="n">
+        <v>-0.8599506376747662</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>1.073806119607655</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.2200963756003317</v>
+      </c>
+      <c r="D304" t="n">
+        <v>-1.268827490154426</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0.09446406873956094</v>
+      </c>
+      <c r="F304" t="n">
+        <v>-0.02874137443549874</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>0.8678187937159658</v>
+      </c>
+      <c r="C305" t="n">
+        <v>-0.2344571971181804</v>
+      </c>
+      <c r="D305" t="n">
+        <v>-0.7142629447502887</v>
+      </c>
+      <c r="E305" t="n">
+        <v>0.1497604137037341</v>
+      </c>
+      <c r="F305" t="n">
+        <v>-0.4774766622463196</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>DR-158</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>1.653050414352565</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.6436565166886825</v>
+      </c>
+      <c r="D306" t="n">
+        <v>1.382076063509662</v>
+      </c>
+      <c r="E306" t="n">
+        <v>-0.6452666640077618</v>
+      </c>
+      <c r="F306" t="n">
+        <v>0.01581010650458104</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>-0.6010929567083756</v>
+      </c>
+      <c r="C307" t="n">
+        <v>-0.3475655255455889</v>
+      </c>
+      <c r="D307" t="n">
+        <v>-2.11441307544067</v>
+      </c>
+      <c r="E307" t="n">
+        <v>-2.144440271813012</v>
+      </c>
+      <c r="F307" t="n">
+        <v>0.463007492135025</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>LSC-64</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>1.074810033192212</v>
+      </c>
+      <c r="C308" t="n">
+        <v>1.7888968436352</v>
+      </c>
+      <c r="D308" t="n">
+        <v>-0.4439619504102208</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0.3498287268194536</v>
+      </c>
+      <c r="F308" t="n">
+        <v>0.1549149409710679</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>LSC-65</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0.6270864727714375</v>
+      </c>
+      <c r="C309" t="n">
+        <v>1.911211248820715</v>
+      </c>
+      <c r="D309" t="n">
+        <v>-0.3439045343652927</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0.2597174492264313</v>
+      </c>
+      <c r="F309" t="n">
+        <v>-0.1730214165750745</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>LSC-66</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>-0.6633848907721112</v>
+      </c>
+      <c r="C310" t="n">
+        <v>1.067861869958231</v>
+      </c>
+      <c r="D310" t="n">
+        <v>-0.3591865961242486</v>
+      </c>
+      <c r="E310" t="n">
+        <v>0.5657141866771584</v>
+      </c>
+      <c r="F310" t="n">
+        <v>0.005953056410717435</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>LSC-67</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>0.660590769354973</v>
+      </c>
+      <c r="C311" t="n">
+        <v>1.999217769256331</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0.1260004171968643</v>
+      </c>
+      <c r="E311" t="n">
+        <v>0.8019405906235675</v>
+      </c>
+      <c r="F311" t="n">
+        <v>-0.6061116917977099</v>
       </c>
     </row>
   </sheetData>
